--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,6 +1653,430 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114785370</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90237</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gallboda, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>696105</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6603197</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen, Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114785431</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90248</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gallboda, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>696325</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6603334</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114785338</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90434</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gallboda, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>696185</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6603284</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen, Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114785543</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90899</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>898</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gallboda, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>696125</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6603246</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen, Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2077,6 +2077,2894 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114947282</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8405</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gallboda (Gallboda), Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>696044</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6602974</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114943662</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95100</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>53</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>696279</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6603358</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114945730</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96507</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>696176</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6603160</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114942139</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5182</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>695999</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6603158</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114944111</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78463</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>696486</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6603333</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114947359</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90250</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gallboda (Gallboda), Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>695995</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6602944</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114947167</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56450</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gallboda (Gallboda), Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>696094</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6603036</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114947683</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79055</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gallboda (Gallboda), Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>695933</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6602894</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114943459</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5162</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>696192</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6603314</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114943342</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90261</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>696202</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6603281</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114947276</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90250</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gallboda (Gallboda), Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>696044</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6602977</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>114947176</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5182</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gallboda (Gallboda), Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>696090</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6603030</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114942675</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90250</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>696089</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6603235</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114942064</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57252</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>695974</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6603093</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>114945342</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5162</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>696394</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6603294</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>114944965</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5162</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>696493</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6603320</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>114944138</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90214</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>696480</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6603339</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>114943271</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90250</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>696144</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6603277</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>114943846</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5345</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>696300</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6603361</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>114941998</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90214</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>695964</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6603110</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>114944951</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8405</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>696494</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6603323</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114942988</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90250</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>696103</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6603210</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>114943970</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5162</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tärnan (Tärnan), Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>696383</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6603316</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114941926</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90214</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>695922</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6603017</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4965,6 +4965,148 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>115040924</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79527</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>695883</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6603246</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Noterade tre intilliggande träd med lunglav</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5107,6 +5107,611 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>115041655</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90263</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>695883</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6603402</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>115041372</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8397</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>695853</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6603332</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>115041348</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8408</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>695852</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6603316</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>115041598</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>695888</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6603409</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>115041615</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8408</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Torpängen (Torpängen), Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>695902</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6603402</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -3439,7 +3439,7 @@
         <v>114943662</v>
       </c>
       <c r="B26" t="n">
-        <v>95384</v>
+        <v>95386</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -5943,10 +5943,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121093817</v>
+        <v>121091232</v>
       </c>
       <c r="B47" t="n">
-        <v>5169</v>
+        <v>90687</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5955,46 +5955,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696239</v>
+        <v>696101</v>
       </c>
       <c r="R47" t="n">
-        <v>6603315</v>
+        <v>6603200</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6021,19 +6016,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6048,22 +6033,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121091232</v>
+        <v>121095556</v>
       </c>
       <c r="B48" t="n">
-        <v>90687</v>
+        <v>57364</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6076,34 +6061,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696101</v>
+        <v>695980</v>
       </c>
       <c r="R48" t="n">
-        <v>6603200</v>
+        <v>6603096</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6274,10 +6264,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121095556</v>
+        <v>121093817</v>
       </c>
       <c r="B50" t="n">
-        <v>57364</v>
+        <v>5169</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6286,31 +6276,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6319,13 +6309,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>695980</v>
+        <v>696239</v>
       </c>
       <c r="R50" t="n">
-        <v>6603096</v>
+        <v>6603315</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6352,9 +6342,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6369,12 +6369,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6941,10 +6941,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121093800</v>
+        <v>121090597</v>
       </c>
       <c r="B56" t="n">
-        <v>57364</v>
+        <v>94690</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6953,46 +6953,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696239</v>
+        <v>695897</v>
       </c>
       <c r="R56" t="n">
-        <v>6603325</v>
+        <v>6603417</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7021,7 +7016,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7031,7 +7026,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7058,10 +7053,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121090597</v>
+        <v>121093800</v>
       </c>
       <c r="B57" t="n">
-        <v>94690</v>
+        <v>57364</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7070,41 +7065,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>695897</v>
+        <v>696239</v>
       </c>
       <c r="R57" t="n">
-        <v>6603417</v>
+        <v>6603325</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8203,10 +8203,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121095125</v>
+        <v>121090488</v>
       </c>
       <c r="B67" t="n">
-        <v>100337</v>
+        <v>79583</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8219,37 +8219,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696122</v>
+        <v>695888</v>
       </c>
       <c r="R67" t="n">
-        <v>6603202</v>
+        <v>6603408</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8276,11 +8276,21 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8289,23 +8299,43 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121093980</v>
+        <v>121095125</v>
       </c>
       <c r="B68" t="n">
         <v>100337</v>
@@ -8345,10 +8375,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696434</v>
+        <v>696122</v>
       </c>
       <c r="R68" t="n">
-        <v>6603315</v>
+        <v>6603202</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8407,10 +8437,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121090488</v>
+        <v>121093980</v>
       </c>
       <c r="B69" t="n">
-        <v>79583</v>
+        <v>100337</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8423,37 +8453,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695888</v>
+        <v>696434</v>
       </c>
       <c r="R69" t="n">
-        <v>6603408</v>
+        <v>6603315</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8480,21 +8510,11 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8503,36 +8523,16 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5831,10 +5831,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121095265</v>
+        <v>121091186</v>
       </c>
       <c r="B46" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696112</v>
+        <v>696070</v>
       </c>
       <c r="R46" t="n">
-        <v>6603209</v>
+        <v>6603197</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5943,10 +5943,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121091232</v>
+        <v>121090637</v>
       </c>
       <c r="B47" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5955,38 +5955,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696101</v>
+        <v>695859</v>
       </c>
       <c r="R47" t="n">
-        <v>6603200</v>
+        <v>6603407</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6045,10 +6045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121095556</v>
+        <v>121095265</v>
       </c>
       <c r="B48" t="n">
-        <v>57364</v>
+        <v>90697</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6061,42 +6061,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695980</v>
+        <v>696112</v>
       </c>
       <c r="R48" t="n">
-        <v>6603096</v>
+        <v>6603209</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6123,9 +6118,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6140,22 +6145,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121091050</v>
+        <v>121090488</v>
       </c>
       <c r="B49" t="n">
-        <v>8421</v>
+        <v>79586</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6168,46 +6173,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106554</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>695927</v>
+        <v>695888</v>
       </c>
       <c r="R49" t="n">
-        <v>6603231</v>
+        <v>6603408</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6234,40 +6230,69 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121093817</v>
+        <v>121090372</v>
       </c>
       <c r="B50" t="n">
-        <v>5169</v>
+        <v>90697</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6276,43 +6301,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696239</v>
+        <v>695883</v>
       </c>
       <c r="R50" t="n">
-        <v>6603315</v>
+        <v>6603408</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6344,7 +6364,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6354,7 +6374,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6381,10 +6401,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121090637</v>
+        <v>121091232</v>
       </c>
       <c r="B51" t="n">
-        <v>100337</v>
+        <v>90697</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6393,38 +6413,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695859</v>
+        <v>696101</v>
       </c>
       <c r="R51" t="n">
-        <v>6603407</v>
+        <v>6603200</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6483,14 +6503,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121090764</v>
+        <v>121095837</v>
       </c>
       <c r="B52" t="n">
-        <v>94474</v>
+        <v>5189</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6499,37 +6519,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2809</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695871</v>
+        <v>695989</v>
       </c>
       <c r="R52" t="n">
-        <v>6603412</v>
+        <v>6603160</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6558,7 +6583,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6568,12 +6593,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6600,10 +6620,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121091319</v>
+        <v>121090442</v>
       </c>
       <c r="B53" t="n">
-        <v>78598</v>
+        <v>79586</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6612,41 +6632,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696097</v>
+        <v>695921</v>
       </c>
       <c r="R53" t="n">
-        <v>6603185</v>
+        <v>6603409</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6673,19 +6693,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6700,22 +6710,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121091126</v>
+        <v>121090910</v>
       </c>
       <c r="B54" t="n">
-        <v>78598</v>
+        <v>100347</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6724,41 +6734,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696034</v>
+        <v>695893</v>
       </c>
       <c r="R54" t="n">
-        <v>6603209</v>
+        <v>6603281</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6785,19 +6795,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6812,22 +6812,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121095299</v>
+        <v>121093980</v>
       </c>
       <c r="B55" t="n">
-        <v>5169</v>
+        <v>100347</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6840,42 +6840,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696094</v>
+        <v>696434</v>
       </c>
       <c r="R55" t="n">
-        <v>6603186</v>
+        <v>6603315</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6902,19 +6897,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6929,22 +6914,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121090597</v>
+        <v>121095556</v>
       </c>
       <c r="B56" t="n">
-        <v>94690</v>
+        <v>57367</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6953,41 +6938,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>695897</v>
+        <v>695980</v>
       </c>
       <c r="R56" t="n">
-        <v>6603417</v>
+        <v>6603096</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7014,19 +7004,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7041,70 +7021,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121093800</v>
+        <v>121090764</v>
       </c>
       <c r="B57" t="n">
-        <v>57364</v>
+        <v>94484</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696239</v>
+        <v>695871</v>
       </c>
       <c r="R57" t="n">
-        <v>6603325</v>
+        <v>6603412</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7133,7 +7108,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7143,7 +7118,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7170,10 +7150,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121093815</v>
+        <v>121091126</v>
       </c>
       <c r="B58" t="n">
-        <v>5189</v>
+        <v>78601</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7182,43 +7162,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696247</v>
+        <v>696034</v>
       </c>
       <c r="R58" t="n">
-        <v>6603313</v>
+        <v>6603209</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7250,7 +7225,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7260,7 +7235,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7287,10 +7262,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121095510</v>
+        <v>121094501</v>
       </c>
       <c r="B59" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7303,21 +7278,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7328,14 +7303,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696021</v>
+        <v>696380</v>
       </c>
       <c r="R59" t="n">
-        <v>6603152</v>
+        <v>6603325</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7367,7 +7342,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7377,7 +7352,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7404,10 +7379,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121092954</v>
+        <v>121099960</v>
       </c>
       <c r="B60" t="n">
-        <v>94737</v>
+        <v>91156</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7416,41 +7391,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2170</v>
+        <v>5467</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696174</v>
+        <v>695863</v>
       </c>
       <c r="R60" t="n">
-        <v>6603210</v>
+        <v>6603398</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7474,22 +7449,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Undersidan av en kraftigt rötad låga</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7500,6 +7480,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7516,10 +7516,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121090910</v>
+        <v>121095299</v>
       </c>
       <c r="B61" t="n">
-        <v>100337</v>
+        <v>5169</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7532,37 +7532,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695893</v>
+        <v>696094</v>
       </c>
       <c r="R61" t="n">
-        <v>6603281</v>
+        <v>6603186</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7589,9 +7594,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7606,22 +7621,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121090372</v>
+        <v>121091319</v>
       </c>
       <c r="B62" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7634,21 +7649,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7658,10 +7673,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>695883</v>
+        <v>696097</v>
       </c>
       <c r="R62" t="n">
-        <v>6603408</v>
+        <v>6603185</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7693,7 +7708,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7703,7 +7718,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7730,10 +7745,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121094501</v>
+        <v>121093973</v>
       </c>
       <c r="B63" t="n">
-        <v>5169</v>
+        <v>91985</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7746,42 +7761,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696380</v>
+        <v>696429</v>
       </c>
       <c r="R63" t="n">
-        <v>6603325</v>
+        <v>6603315</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7808,19 +7818,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7835,22 +7835,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121099960</v>
+        <v>121093800</v>
       </c>
       <c r="B64" t="n">
-        <v>91146</v>
+        <v>57367</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7863,37 +7863,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5467</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>695863</v>
+        <v>696239</v>
       </c>
       <c r="R64" t="n">
-        <v>6603398</v>
+        <v>6603325</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7917,27 +7922,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Undersidan av en kraftigt rötad låga</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7948,26 +7948,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7984,10 +7964,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121094438</v>
+        <v>121092954</v>
       </c>
       <c r="B65" t="n">
-        <v>5169</v>
+        <v>94747</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8000,42 +7980,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696484</v>
+        <v>696174</v>
       </c>
       <c r="R65" t="n">
-        <v>6603311</v>
+        <v>6603210</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8064,7 +8039,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8074,7 +8049,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8104,7 +8079,7 @@
         <v>121091204</v>
       </c>
       <c r="B66" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8203,10 +8178,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121090488</v>
+        <v>121090597</v>
       </c>
       <c r="B67" t="n">
-        <v>79583</v>
+        <v>94700</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8219,21 +8194,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>210</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8243,10 +8218,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>695888</v>
+        <v>695897</v>
       </c>
       <c r="R67" t="n">
-        <v>6603408</v>
+        <v>6603417</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8278,7 +8253,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8288,7 +8263,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8299,26 +8274,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8335,10 +8290,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121095125</v>
+        <v>121091050</v>
       </c>
       <c r="B68" t="n">
-        <v>100337</v>
+        <v>8421</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8351,34 +8306,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696122</v>
+        <v>695927</v>
       </c>
       <c r="R68" t="n">
-        <v>6603202</v>
+        <v>6603231</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8419,6 +8383,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8437,10 +8402,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121093980</v>
+        <v>121093815</v>
       </c>
       <c r="B69" t="n">
-        <v>100337</v>
+        <v>5189</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8453,37 +8418,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696434</v>
+        <v>696247</v>
       </c>
       <c r="R69" t="n">
-        <v>6603315</v>
+        <v>6603313</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8510,9 +8480,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8527,22 +8507,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121093973</v>
+        <v>121095510</v>
       </c>
       <c r="B70" t="n">
-        <v>91975</v>
+        <v>5189</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8555,37 +8535,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4366</v>
+        <v>105930</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696429</v>
+        <v>696021</v>
       </c>
       <c r="R70" t="n">
-        <v>6603315</v>
+        <v>6603152</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8612,9 +8597,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8629,22 +8624,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121095837</v>
+        <v>121094438</v>
       </c>
       <c r="B71" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8657,21 +8652,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8682,14 +8677,14 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695989</v>
+        <v>696484</v>
       </c>
       <c r="R71" t="n">
-        <v>6603160</v>
+        <v>6603311</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8721,7 +8716,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8731,7 +8726,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8758,10 +8753,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121091186</v>
+        <v>121095125</v>
       </c>
       <c r="B72" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8770,41 +8765,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696070</v>
+        <v>696122</v>
       </c>
       <c r="R72" t="n">
-        <v>6603197</v>
+        <v>6603202</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8831,19 +8826,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8858,22 +8843,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121090442</v>
+        <v>121090573</v>
       </c>
       <c r="B73" t="n">
-        <v>79583</v>
+        <v>94700</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8886,34 +8871,43 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6456</v>
+        <v>210</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>695921</v>
+        <v>695901</v>
       </c>
       <c r="R73" t="n">
-        <v>6603409</v>
+        <v>6603407</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8972,10 +8966,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121090573</v>
+        <v>121093817</v>
       </c>
       <c r="B74" t="n">
-        <v>94690</v>
+        <v>5169</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8988,46 +8982,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>210</v>
+        <v>100526</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695901</v>
+        <v>696239</v>
       </c>
       <c r="R74" t="n">
-        <v>6603407</v>
+        <v>6603315</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9054,9 +9044,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9071,12 +9071,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
         <v>121090765</v>
       </c>
       <c r="B75" t="n">
-        <v>94474</v>
+        <v>94484</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9182,6 +9182,1961 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>121404815</v>
+      </c>
+      <c r="B76" t="n">
+        <v>94484</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>695864</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6603266</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>121402388</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>695971</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6603090</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>121402361</v>
+      </c>
+      <c r="B78" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>696010</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6603109</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>121404558</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Torpängen, Torpängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>695865</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6603318</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>121402709</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>696025</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6603166</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>121405386</v>
+      </c>
+      <c r="B81" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>696099</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6603163</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>121404366</v>
+      </c>
+      <c r="B82" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>695857</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6603366</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>121404209</v>
+      </c>
+      <c r="B83" t="n">
+        <v>94484</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>695935</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6603415</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>121404249</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>695896</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6603382</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>121402809</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>696135</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6603162</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>121404293</v>
+      </c>
+      <c r="B86" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>695856</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6603367</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>121404898</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8421</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>696024</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6603210</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>121404539</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>695869</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6603281</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>121404569</v>
+      </c>
+      <c r="B89" t="n">
+        <v>4772</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>695858</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6603299</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>121403961</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79682</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Torpängen, Torpängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>695886</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6603243</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>121404545</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>695870</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6603295</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>121405694</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Torpängen, Torpängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>695999</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6603117</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>121402734</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Torpängen, Torpängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>696145</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6603212</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -5943,10 +5943,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121090637</v>
+        <v>121095265</v>
       </c>
       <c r="B47" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5955,41 +5955,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695859</v>
+        <v>696112</v>
       </c>
       <c r="R47" t="n">
-        <v>6603407</v>
+        <v>6603209</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6016,9 +6016,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6033,22 +6043,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121095265</v>
+        <v>121090637</v>
       </c>
       <c r="B48" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6057,41 +6067,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696112</v>
+        <v>695859</v>
       </c>
       <c r="R48" t="n">
-        <v>6603209</v>
+        <v>6603407</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6118,19 +6128,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6145,12 +6145,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6401,10 +6401,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121091232</v>
+        <v>121090442</v>
       </c>
       <c r="B51" t="n">
-        <v>90697</v>
+        <v>79586</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6413,38 +6413,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696101</v>
+        <v>695921</v>
       </c>
       <c r="R51" t="n">
-        <v>6603200</v>
+        <v>6603409</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6620,10 +6620,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121090442</v>
+        <v>121091232</v>
       </c>
       <c r="B53" t="n">
-        <v>79586</v>
+        <v>90697</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6632,38 +6632,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>695921</v>
+        <v>696101</v>
       </c>
       <c r="R53" t="n">
-        <v>6603409</v>
+        <v>6603200</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -10790,10 +10790,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121404545</v>
+        <v>121405694</v>
       </c>
       <c r="B91" t="n">
-        <v>8432</v>
+        <v>98081</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10802,38 +10802,52 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695870</v>
+        <v>695999</v>
       </c>
       <c r="R91" t="n">
-        <v>6603295</v>
+        <v>6603117</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10863,9 +10877,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10880,22 +10909,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121405694</v>
+        <v>121404545</v>
       </c>
       <c r="B92" t="n">
-        <v>98081</v>
+        <v>8432</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10904,52 +10933,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695999</v>
+        <v>695870</v>
       </c>
       <c r="R92" t="n">
-        <v>6603117</v>
+        <v>6603295</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10979,24 +10994,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11011,12 +11011,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -5943,10 +5943,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121095265</v>
+        <v>121090637</v>
       </c>
       <c r="B47" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5955,41 +5955,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696112</v>
+        <v>695859</v>
       </c>
       <c r="R47" t="n">
-        <v>6603209</v>
+        <v>6603407</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6016,19 +6016,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6043,22 +6033,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121090637</v>
+        <v>121095265</v>
       </c>
       <c r="B48" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6067,41 +6057,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695859</v>
+        <v>696112</v>
       </c>
       <c r="R48" t="n">
-        <v>6603407</v>
+        <v>6603209</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6128,9 +6118,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6145,12 +6145,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6401,10 +6401,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121090442</v>
+        <v>121091232</v>
       </c>
       <c r="B51" t="n">
-        <v>79586</v>
+        <v>90697</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6413,38 +6413,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695921</v>
+        <v>696101</v>
       </c>
       <c r="R51" t="n">
-        <v>6603409</v>
+        <v>6603200</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6620,10 +6620,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121091232</v>
+        <v>121090442</v>
       </c>
       <c r="B53" t="n">
-        <v>90697</v>
+        <v>79586</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6632,38 +6632,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696101</v>
+        <v>695921</v>
       </c>
       <c r="R53" t="n">
-        <v>6603200</v>
+        <v>6603409</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -5831,10 +5831,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121091186</v>
+        <v>121090573</v>
       </c>
       <c r="B46" t="n">
-        <v>90697</v>
+        <v>94700</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5843,41 +5843,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696070</v>
+        <v>695901</v>
       </c>
       <c r="R46" t="n">
-        <v>6603197</v>
+        <v>6603407</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5904,19 +5913,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5931,22 +5930,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121090637</v>
+        <v>121091232</v>
       </c>
       <c r="B47" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5955,38 +5954,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695859</v>
+        <v>696101</v>
       </c>
       <c r="R47" t="n">
-        <v>6603407</v>
+        <v>6603200</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6045,7 +6044,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121095265</v>
+        <v>121091186</v>
       </c>
       <c r="B48" t="n">
         <v>90697</v>
@@ -6085,10 +6084,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696112</v>
+        <v>696070</v>
       </c>
       <c r="R48" t="n">
-        <v>6603209</v>
+        <v>6603197</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6120,7 +6119,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6130,7 +6129,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6157,10 +6156,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121090488</v>
+        <v>121090372</v>
       </c>
       <c r="B49" t="n">
-        <v>79586</v>
+        <v>90697</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6169,25 +6168,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6197,7 +6196,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>695888</v>
+        <v>695883</v>
       </c>
       <c r="R49" t="n">
         <v>6603408</v>
@@ -6232,7 +6231,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6242,7 +6241,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6253,26 +6252,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6289,10 +6268,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121090372</v>
+        <v>121095556</v>
       </c>
       <c r="B50" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6305,37 +6284,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>695883</v>
+        <v>695980</v>
       </c>
       <c r="R50" t="n">
-        <v>6603408</v>
+        <v>6603096</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6362,19 +6346,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>09:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6389,22 +6363,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121091232</v>
+        <v>121093817</v>
       </c>
       <c r="B51" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6413,41 +6387,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696101</v>
+        <v>696239</v>
       </c>
       <c r="R51" t="n">
-        <v>6603200</v>
+        <v>6603315</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6474,9 +6453,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6491,12 +6480,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6620,10 +6609,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121090442</v>
+        <v>121091126</v>
       </c>
       <c r="B53" t="n">
-        <v>79586</v>
+        <v>78601</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6632,41 +6621,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>695921</v>
+        <v>696034</v>
       </c>
       <c r="R53" t="n">
-        <v>6603409</v>
+        <v>6603209</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6693,9 +6682,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6710,22 +6709,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121090910</v>
+        <v>121091319</v>
       </c>
       <c r="B54" t="n">
-        <v>100347</v>
+        <v>78601</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6734,41 +6733,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>695893</v>
+        <v>696097</v>
       </c>
       <c r="R54" t="n">
-        <v>6603281</v>
+        <v>6603185</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6795,9 +6794,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6812,22 +6821,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121093980</v>
+        <v>121095299</v>
       </c>
       <c r="B55" t="n">
-        <v>100347</v>
+        <v>5169</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6840,37 +6849,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696434</v>
+        <v>696094</v>
       </c>
       <c r="R55" t="n">
-        <v>6603315</v>
+        <v>6603186</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6897,9 +6911,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6914,22 +6938,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121095556</v>
+        <v>121095510</v>
       </c>
       <c r="B56" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6938,20 +6962,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6962,22 +6986,22 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>695980</v>
+        <v>696021</v>
       </c>
       <c r="R56" t="n">
-        <v>6603096</v>
+        <v>6603152</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7004,9 +7028,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7021,65 +7055,70 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121090764</v>
+        <v>121093800</v>
       </c>
       <c r="B57" t="n">
-        <v>94484</v>
+        <v>57367</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>695871</v>
+        <v>696239</v>
       </c>
       <c r="R57" t="n">
-        <v>6603412</v>
+        <v>6603325</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7108,7 +7147,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7118,12 +7157,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7150,10 +7184,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121091126</v>
+        <v>121092954</v>
       </c>
       <c r="B58" t="n">
-        <v>78601</v>
+        <v>94747</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7162,41 +7196,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696034</v>
+        <v>696174</v>
       </c>
       <c r="R58" t="n">
-        <v>6603209</v>
+        <v>6603210</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7225,7 +7259,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7235,7 +7269,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7262,7 +7296,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121094501</v>
+        <v>121094438</v>
       </c>
       <c r="B59" t="n">
         <v>5169</v>
@@ -7307,10 +7341,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696380</v>
+        <v>696484</v>
       </c>
       <c r="R59" t="n">
-        <v>6603325</v>
+        <v>6603311</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7342,7 +7376,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7352,7 +7386,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7379,10 +7413,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121099960</v>
+        <v>121090597</v>
       </c>
       <c r="B60" t="n">
-        <v>91156</v>
+        <v>94700</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7391,25 +7425,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5467</v>
+        <v>210</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7419,13 +7453,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695863</v>
+        <v>695897</v>
       </c>
       <c r="R60" t="n">
-        <v>6603398</v>
+        <v>6603417</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7449,27 +7483,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Undersidan av en kraftigt rötad låga</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7480,26 +7509,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7516,10 +7525,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121095299</v>
+        <v>121095265</v>
       </c>
       <c r="B61" t="n">
-        <v>5169</v>
+        <v>90697</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7528,43 +7537,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696094</v>
+        <v>696112</v>
       </c>
       <c r="R61" t="n">
-        <v>6603186</v>
+        <v>6603209</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7633,37 +7637,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121091319</v>
+        <v>121090764</v>
       </c>
       <c r="B62" t="n">
-        <v>78601</v>
+        <v>94484</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7673,13 +7677,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696097</v>
+        <v>695871</v>
       </c>
       <c r="R62" t="n">
-        <v>6603185</v>
+        <v>6603412</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7708,7 +7712,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7718,7 +7722,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7745,10 +7754,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121093973</v>
+        <v>121090910</v>
       </c>
       <c r="B63" t="n">
-        <v>91985</v>
+        <v>100347</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7761,34 +7770,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696429</v>
+        <v>695893</v>
       </c>
       <c r="R63" t="n">
-        <v>6603315</v>
+        <v>6603281</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7847,10 +7856,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121093800</v>
+        <v>121093973</v>
       </c>
       <c r="B64" t="n">
-        <v>57367</v>
+        <v>91985</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7859,46 +7868,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>696239</v>
+        <v>696429</v>
       </c>
       <c r="R64" t="n">
-        <v>6603325</v>
+        <v>6603315</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7925,19 +7929,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7952,22 +7946,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121092954</v>
+        <v>121094501</v>
       </c>
       <c r="B65" t="n">
-        <v>94747</v>
+        <v>5169</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7980,37 +7974,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696174</v>
+        <v>696380</v>
       </c>
       <c r="R65" t="n">
-        <v>6603210</v>
+        <v>6603325</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8039,7 +8038,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8049,7 +8048,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8076,10 +8075,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121091204</v>
+        <v>121090442</v>
       </c>
       <c r="B66" t="n">
-        <v>100347</v>
+        <v>79586</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8092,34 +8091,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696104</v>
+        <v>695921</v>
       </c>
       <c r="R66" t="n">
-        <v>6603207</v>
+        <v>6603409</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8178,10 +8177,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121090597</v>
+        <v>121095125</v>
       </c>
       <c r="B67" t="n">
-        <v>94700</v>
+        <v>100347</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8194,37 +8193,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>695897</v>
+        <v>696122</v>
       </c>
       <c r="R67" t="n">
-        <v>6603417</v>
+        <v>6603202</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8251,19 +8250,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8278,22 +8267,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121091050</v>
+        <v>121090637</v>
       </c>
       <c r="B68" t="n">
-        <v>8421</v>
+        <v>100347</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8306,43 +8295,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>695927</v>
+        <v>695859</v>
       </c>
       <c r="R68" t="n">
-        <v>6603231</v>
+        <v>6603407</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8383,7 +8363,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8402,10 +8381,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121093815</v>
+        <v>121093980</v>
       </c>
       <c r="B69" t="n">
-        <v>5189</v>
+        <v>100347</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8418,42 +8397,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696247</v>
+        <v>696434</v>
       </c>
       <c r="R69" t="n">
-        <v>6603313</v>
+        <v>6603315</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8480,19 +8454,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>11:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8507,22 +8471,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121095510</v>
+        <v>121090488</v>
       </c>
       <c r="B70" t="n">
-        <v>5189</v>
+        <v>79586</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8535,39 +8499,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>105930</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696021</v>
+        <v>695888</v>
       </c>
       <c r="R70" t="n">
-        <v>6603152</v>
+        <v>6603408</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8599,7 +8558,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8609,7 +8568,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8620,6 +8579,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8636,10 +8615,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121094438</v>
+        <v>121099960</v>
       </c>
       <c r="B71" t="n">
-        <v>5169</v>
+        <v>91156</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8648,46 +8627,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>5467</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>696484</v>
+        <v>695863</v>
       </c>
       <c r="R71" t="n">
-        <v>6603311</v>
+        <v>6603398</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8711,22 +8685,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Undersidan av en kraftigt rötad låga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8737,6 +8716,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8753,7 +8752,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121095125</v>
+        <v>121091204</v>
       </c>
       <c r="B72" t="n">
         <v>100347</v>
@@ -8793,10 +8792,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696122</v>
+        <v>696104</v>
       </c>
       <c r="R72" t="n">
-        <v>6603202</v>
+        <v>6603207</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8855,10 +8854,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121090573</v>
+        <v>121091050</v>
       </c>
       <c r="B73" t="n">
-        <v>94700</v>
+        <v>8421</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8871,43 +8870,43 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>695901</v>
+        <v>695927</v>
       </c>
       <c r="R73" t="n">
-        <v>6603407</v>
+        <v>6603231</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8948,6 +8947,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8966,10 +8966,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121093817</v>
+        <v>121093815</v>
       </c>
       <c r="B74" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8982,21 +8982,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696239</v>
+        <v>696247</v>
       </c>
       <c r="R74" t="n">
-        <v>6603315</v>
+        <v>6603313</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -9185,10 +9185,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121404815</v>
+        <v>121402734</v>
       </c>
       <c r="B76" t="n">
-        <v>94484</v>
+        <v>57367</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9197,38 +9197,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695864</v>
+        <v>696145</v>
       </c>
       <c r="R76" t="n">
-        <v>6603266</v>
+        <v>6603212</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9258,9 +9263,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9275,19 +9290,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121402388</v>
+        <v>121404558</v>
       </c>
       <c r="B77" t="n">
         <v>57367</v>
@@ -9323,19 +9338,19 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695971</v>
+        <v>695865</v>
       </c>
       <c r="R77" t="n">
-        <v>6603090</v>
+        <v>6603318</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9365,9 +9380,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9382,22 +9407,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402361</v>
+        <v>121402388</v>
       </c>
       <c r="B78" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9406,43 +9431,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696010</v>
+        <v>695971</v>
       </c>
       <c r="R78" t="n">
-        <v>6603109</v>
+        <v>6603090</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9501,7 +9526,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404558</v>
+        <v>121402709</v>
       </c>
       <c r="B79" t="n">
         <v>57367</v>
@@ -9537,19 +9562,19 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695865</v>
+        <v>696025</v>
       </c>
       <c r="R79" t="n">
-        <v>6603318</v>
+        <v>6603166</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9579,19 +9604,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,22 +9621,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121402709</v>
+        <v>121405694</v>
       </c>
       <c r="B80" t="n">
-        <v>57367</v>
+        <v>98081</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9630,43 +9645,52 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696025</v>
+        <v>695999</v>
       </c>
       <c r="R80" t="n">
-        <v>6603166</v>
+        <v>6603117</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9696,9 +9720,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9713,22 +9752,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121405386</v>
+        <v>121403961</v>
       </c>
       <c r="B81" t="n">
-        <v>90662</v>
+        <v>79682</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9737,38 +9776,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>696099</v>
+        <v>695886</v>
       </c>
       <c r="R81" t="n">
-        <v>6603163</v>
+        <v>6603243</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9798,9 +9837,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9815,22 +9869,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404366</v>
+        <v>121404898</v>
       </c>
       <c r="B82" t="n">
-        <v>90697</v>
+        <v>8421</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9839,38 +9893,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695857</v>
+        <v>696024</v>
       </c>
       <c r="R82" t="n">
-        <v>6603366</v>
+        <v>6603210</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9929,10 +9988,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404209</v>
+        <v>121402361</v>
       </c>
       <c r="B83" t="n">
-        <v>94484</v>
+        <v>5169</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9945,34 +10004,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695935</v>
+        <v>696010</v>
       </c>
       <c r="R83" t="n">
-        <v>6603415</v>
+        <v>6603109</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10031,10 +10095,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404249</v>
+        <v>121404569</v>
       </c>
       <c r="B84" t="n">
-        <v>57367</v>
+        <v>4772</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10043,31 +10107,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10076,10 +10140,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695896</v>
+        <v>695858</v>
       </c>
       <c r="R84" t="n">
-        <v>6603382</v>
+        <v>6603299</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10138,10 +10202,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121402809</v>
+        <v>121405386</v>
       </c>
       <c r="B85" t="n">
-        <v>57367</v>
+        <v>90662</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10150,43 +10214,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>696135</v>
+        <v>696099</v>
       </c>
       <c r="R85" t="n">
-        <v>6603162</v>
+        <v>6603163</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10245,10 +10304,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404293</v>
+        <v>121404366</v>
       </c>
       <c r="B86" t="n">
-        <v>5169</v>
+        <v>90697</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10257,43 +10316,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695856</v>
+        <v>695857</v>
       </c>
       <c r="R86" t="n">
-        <v>6603367</v>
+        <v>6603366</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10352,10 +10406,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404898</v>
+        <v>121404545</v>
       </c>
       <c r="B87" t="n">
-        <v>8421</v>
+        <v>8432</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10368,39 +10422,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>696024</v>
+        <v>695870</v>
       </c>
       <c r="R87" t="n">
-        <v>6603210</v>
+        <v>6603295</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10459,10 +10508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404539</v>
+        <v>121404293</v>
       </c>
       <c r="B88" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10471,31 +10520,31 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10504,10 +10553,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695869</v>
+        <v>695856</v>
       </c>
       <c r="R88" t="n">
-        <v>6603281</v>
+        <v>6603367</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10566,10 +10615,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121404569</v>
+        <v>121402809</v>
       </c>
       <c r="B89" t="n">
-        <v>4772</v>
+        <v>57367</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10578,43 +10627,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>695858</v>
+        <v>696135</v>
       </c>
       <c r="R89" t="n">
-        <v>6603299</v>
+        <v>6603162</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10673,10 +10722,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121403961</v>
+        <v>121404539</v>
       </c>
       <c r="B90" t="n">
-        <v>79682</v>
+        <v>57367</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10689,34 +10738,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695886</v>
+        <v>695869</v>
       </c>
       <c r="R90" t="n">
-        <v>6603243</v>
+        <v>6603281</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10746,24 +10800,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10778,22 +10817,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121405694</v>
+        <v>121404249</v>
       </c>
       <c r="B91" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10802,52 +10841,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695999</v>
+        <v>695896</v>
       </c>
       <c r="R91" t="n">
-        <v>6603117</v>
+        <v>6603382</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10877,24 +10907,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10909,22 +10924,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121404545</v>
+        <v>121404815</v>
       </c>
       <c r="B92" t="n">
-        <v>8432</v>
+        <v>94484</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10937,21 +10952,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>2809</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10961,10 +10976,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695870</v>
+        <v>695864</v>
       </c>
       <c r="R92" t="n">
-        <v>6603295</v>
+        <v>6603266</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11023,10 +11038,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121402734</v>
+        <v>121404209</v>
       </c>
       <c r="B93" t="n">
-        <v>57367</v>
+        <v>94484</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11035,43 +11050,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>696145</v>
+        <v>695935</v>
       </c>
       <c r="R93" t="n">
-        <v>6603212</v>
+        <v>6603415</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11101,19 +11111,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11128,12 +11128,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -6492,10 +6492,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121095837</v>
+        <v>121091126</v>
       </c>
       <c r="B52" t="n">
-        <v>5189</v>
+        <v>78601</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6504,43 +6504,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695989</v>
+        <v>696034</v>
       </c>
       <c r="R52" t="n">
-        <v>6603160</v>
+        <v>6603209</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6572,7 +6567,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6582,7 +6577,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6609,10 +6604,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121091126</v>
+        <v>121095837</v>
       </c>
       <c r="B53" t="n">
-        <v>78601</v>
+        <v>5189</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6621,38 +6616,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696034</v>
+        <v>695989</v>
       </c>
       <c r="R53" t="n">
-        <v>6603209</v>
+        <v>6603160</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6950,10 +6950,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121095510</v>
+        <v>121093800</v>
       </c>
       <c r="B56" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6962,20 +6962,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6986,22 +6986,22 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696021</v>
+        <v>696239</v>
       </c>
       <c r="R56" t="n">
-        <v>6603152</v>
+        <v>6603325</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7067,10 +7067,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121093800</v>
+        <v>121095510</v>
       </c>
       <c r="B57" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7079,20 +7079,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7103,22 +7103,22 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696239</v>
+        <v>696021</v>
       </c>
       <c r="R57" t="n">
-        <v>6603325</v>
+        <v>6603152</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7637,14 +7637,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121090764</v>
+        <v>121093973</v>
       </c>
       <c r="B62" t="n">
-        <v>94484</v>
+        <v>91985</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7653,37 +7653,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2809</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>695871</v>
+        <v>696429</v>
       </c>
       <c r="R62" t="n">
-        <v>6603412</v>
+        <v>6603315</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7710,24 +7710,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7742,26 +7727,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121090910</v>
+        <v>121090764</v>
       </c>
       <c r="B63" t="n">
-        <v>100347</v>
+        <v>94484</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7770,37 +7755,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>695893</v>
+        <v>695871</v>
       </c>
       <c r="R63" t="n">
-        <v>6603281</v>
+        <v>6603412</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7827,9 +7812,24 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7844,22 +7844,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121093973</v>
+        <v>121094501</v>
       </c>
       <c r="B64" t="n">
-        <v>91985</v>
+        <v>5169</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7872,37 +7872,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>696429</v>
+        <v>696380</v>
       </c>
       <c r="R64" t="n">
-        <v>6603315</v>
+        <v>6603325</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7929,9 +7934,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7946,22 +7961,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121094501</v>
+        <v>121090910</v>
       </c>
       <c r="B65" t="n">
-        <v>5169</v>
+        <v>100347</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7974,42 +7989,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696380</v>
+        <v>695893</v>
       </c>
       <c r="R65" t="n">
-        <v>6603325</v>
+        <v>6603281</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8036,19 +8046,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8063,22 +8063,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121090442</v>
+        <v>121095125</v>
       </c>
       <c r="B66" t="n">
-        <v>79586</v>
+        <v>100347</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8091,34 +8091,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>695921</v>
+        <v>696122</v>
       </c>
       <c r="R66" t="n">
-        <v>6603409</v>
+        <v>6603202</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8177,10 +8177,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121095125</v>
+        <v>121090442</v>
       </c>
       <c r="B67" t="n">
-        <v>100347</v>
+        <v>79586</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8193,34 +8193,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696122</v>
+        <v>695921</v>
       </c>
       <c r="R67" t="n">
-        <v>6603202</v>
+        <v>6603409</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -10406,10 +10406,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404545</v>
+        <v>121404293</v>
       </c>
       <c r="B87" t="n">
-        <v>8432</v>
+        <v>5169</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10422,34 +10422,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695870</v>
+        <v>695856</v>
       </c>
       <c r="R87" t="n">
-        <v>6603295</v>
+        <v>6603367</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10508,10 +10513,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404293</v>
+        <v>121404545</v>
       </c>
       <c r="B88" t="n">
-        <v>5169</v>
+        <v>8432</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10524,39 +10529,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695856</v>
+        <v>695870</v>
       </c>
       <c r="R88" t="n">
-        <v>6603367</v>
+        <v>6603295</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -5831,10 +5831,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121090573</v>
+        <v>121090488</v>
       </c>
       <c r="B46" t="n">
-        <v>94700</v>
+        <v>79589</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5847,46 +5847,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695901</v>
+        <v>695888</v>
       </c>
       <c r="R46" t="n">
-        <v>6603407</v>
+        <v>6603408</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5913,11 +5904,21 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5926,26 +5927,46 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121091232</v>
+        <v>121091050</v>
       </c>
       <c r="B47" t="n">
-        <v>90697</v>
+        <v>8421</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5954,38 +5975,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696101</v>
+        <v>695927</v>
       </c>
       <c r="R47" t="n">
-        <v>6603200</v>
+        <v>6603231</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6026,6 +6056,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6044,10 +6075,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121091186</v>
+        <v>121093817</v>
       </c>
       <c r="B48" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6056,38 +6087,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696070</v>
+        <v>696239</v>
       </c>
       <c r="R48" t="n">
-        <v>6603197</v>
+        <v>6603315</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6119,7 +6155,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6129,7 +6165,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6156,10 +6192,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121090372</v>
+        <v>121094501</v>
       </c>
       <c r="B49" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6168,38 +6204,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>695883</v>
+        <v>696380</v>
       </c>
       <c r="R49" t="n">
-        <v>6603408</v>
+        <v>6603325</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6231,7 +6272,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6241,7 +6282,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6268,10 +6309,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121095556</v>
+        <v>121090442</v>
       </c>
       <c r="B50" t="n">
-        <v>57367</v>
+        <v>79589</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6280,43 +6321,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>695980</v>
+        <v>695921</v>
       </c>
       <c r="R50" t="n">
-        <v>6603096</v>
+        <v>6603409</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6375,10 +6411,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121093817</v>
+        <v>121090597</v>
       </c>
       <c r="B51" t="n">
-        <v>5169</v>
+        <v>94712</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6391,39 +6427,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>210</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696239</v>
+        <v>695897</v>
       </c>
       <c r="R51" t="n">
-        <v>6603315</v>
+        <v>6603417</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6455,7 +6486,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6465,7 +6496,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6492,10 +6523,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121091126</v>
+        <v>121092954</v>
       </c>
       <c r="B52" t="n">
-        <v>78601</v>
+        <v>94759</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6504,41 +6535,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696034</v>
+        <v>696174</v>
       </c>
       <c r="R52" t="n">
-        <v>6603209</v>
+        <v>6603210</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6567,7 +6598,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6577,7 +6608,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6604,10 +6635,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121095837</v>
+        <v>121090910</v>
       </c>
       <c r="B53" t="n">
-        <v>5189</v>
+        <v>100360</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6620,42 +6651,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>695989</v>
+        <v>695893</v>
       </c>
       <c r="R53" t="n">
-        <v>6603160</v>
+        <v>6603281</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6682,19 +6708,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6709,22 +6725,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121091319</v>
+        <v>121095299</v>
       </c>
       <c r="B54" t="n">
-        <v>78601</v>
+        <v>5169</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6733,38 +6749,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696097</v>
+        <v>696094</v>
       </c>
       <c r="R54" t="n">
-        <v>6603185</v>
+        <v>6603186</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6796,7 +6817,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6806,7 +6827,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6833,10 +6854,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121095299</v>
+        <v>121090372</v>
       </c>
       <c r="B55" t="n">
-        <v>5169</v>
+        <v>90709</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6845,43 +6866,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696094</v>
+        <v>695883</v>
       </c>
       <c r="R55" t="n">
-        <v>6603186</v>
+        <v>6603408</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6913,7 +6929,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6923,7 +6939,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6950,10 +6966,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121093800</v>
+        <v>121094438</v>
       </c>
       <c r="B56" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6962,31 +6978,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6995,13 +7011,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696239</v>
+        <v>696484</v>
       </c>
       <c r="R56" t="n">
-        <v>6603325</v>
+        <v>6603311</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7030,7 +7046,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7040,7 +7056,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7067,7 +7083,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121095510</v>
+        <v>121093815</v>
       </c>
       <c r="B57" t="n">
         <v>5189</v>
@@ -7108,14 +7124,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696021</v>
+        <v>696247</v>
       </c>
       <c r="R57" t="n">
-        <v>6603152</v>
+        <v>6603313</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7147,7 +7163,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7157,7 +7173,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7184,10 +7200,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121092954</v>
+        <v>121091204</v>
       </c>
       <c r="B58" t="n">
-        <v>94747</v>
+        <v>100360</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7200,21 +7216,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2170</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7224,13 +7240,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696174</v>
+        <v>696104</v>
       </c>
       <c r="R58" t="n">
-        <v>6603210</v>
+        <v>6603207</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7257,19 +7273,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7284,22 +7290,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121094438</v>
+        <v>121095556</v>
       </c>
       <c r="B59" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7308,31 +7314,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7341,13 +7347,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696484</v>
+        <v>695980</v>
       </c>
       <c r="R59" t="n">
-        <v>6603311</v>
+        <v>6603096</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7374,19 +7380,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7401,22 +7397,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121090597</v>
+        <v>121093800</v>
       </c>
       <c r="B60" t="n">
-        <v>94700</v>
+        <v>57367</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7425,41 +7421,46 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695897</v>
+        <v>696239</v>
       </c>
       <c r="R60" t="n">
-        <v>6603417</v>
+        <v>6603325</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7488,7 +7489,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7498,7 +7499,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7525,10 +7526,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121095265</v>
+        <v>121093980</v>
       </c>
       <c r="B61" t="n">
-        <v>90697</v>
+        <v>100360</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7537,41 +7538,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696112</v>
+        <v>696434</v>
       </c>
       <c r="R61" t="n">
-        <v>6603209</v>
+        <v>6603315</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7598,19 +7599,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7625,22 +7616,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121093973</v>
+        <v>121095265</v>
       </c>
       <c r="B62" t="n">
-        <v>91985</v>
+        <v>90709</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7649,41 +7640,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696429</v>
+        <v>696112</v>
       </c>
       <c r="R62" t="n">
-        <v>6603315</v>
+        <v>6603209</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7710,9 +7701,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7727,26 +7728,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121090764</v>
+        <v>121095837</v>
       </c>
       <c r="B63" t="n">
-        <v>94484</v>
+        <v>5189</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7755,37 +7756,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2809</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>695871</v>
+        <v>695989</v>
       </c>
       <c r="R63" t="n">
-        <v>6603412</v>
+        <v>6603160</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7814,7 +7820,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7824,12 +7830,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7856,10 +7857,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121094501</v>
+        <v>121090637</v>
       </c>
       <c r="B64" t="n">
-        <v>5169</v>
+        <v>100360</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7872,42 +7873,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>696380</v>
+        <v>695859</v>
       </c>
       <c r="R64" t="n">
-        <v>6603325</v>
+        <v>6603407</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7934,19 +7930,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7961,22 +7947,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121090910</v>
+        <v>121091232</v>
       </c>
       <c r="B65" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7985,38 +7971,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>695893</v>
+        <v>696101</v>
       </c>
       <c r="R65" t="n">
-        <v>6603281</v>
+        <v>6603200</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8078,7 +8064,7 @@
         <v>121095125</v>
       </c>
       <c r="B66" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8177,10 +8163,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121090442</v>
+        <v>121093973</v>
       </c>
       <c r="B67" t="n">
-        <v>79586</v>
+        <v>91997</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8193,34 +8179,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>4366</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>695921</v>
+        <v>696429</v>
       </c>
       <c r="R67" t="n">
-        <v>6603409</v>
+        <v>6603315</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8279,14 +8265,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121090637</v>
+        <v>121090764</v>
       </c>
       <c r="B68" t="n">
-        <v>100347</v>
+        <v>94496</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8295,37 +8281,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>695859</v>
+        <v>695871</v>
       </c>
       <c r="R68" t="n">
-        <v>6603407</v>
+        <v>6603412</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8352,9 +8338,24 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8369,22 +8370,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121093980</v>
+        <v>121095510</v>
       </c>
       <c r="B69" t="n">
-        <v>100347</v>
+        <v>5189</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8397,37 +8398,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696434</v>
+        <v>696021</v>
       </c>
       <c r="R69" t="n">
-        <v>6603315</v>
+        <v>6603152</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8454,9 +8460,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8471,22 +8487,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121090488</v>
+        <v>121091126</v>
       </c>
       <c r="B70" t="n">
-        <v>79586</v>
+        <v>78604</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8495,25 +8511,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8523,10 +8539,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695888</v>
+        <v>696034</v>
       </c>
       <c r="R70" t="n">
-        <v>6603408</v>
+        <v>6603209</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8558,7 +8574,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8568,7 +8584,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8579,26 +8595,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8615,10 +8611,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121099960</v>
+        <v>121091186</v>
       </c>
       <c r="B71" t="n">
-        <v>91156</v>
+        <v>90709</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8631,21 +8627,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5467</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8655,13 +8651,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695863</v>
+        <v>696070</v>
       </c>
       <c r="R71" t="n">
-        <v>6603398</v>
+        <v>6603197</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8685,27 +8681,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Undersidan av en kraftigt rötad låga</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8716,26 +8707,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8752,10 +8723,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121091204</v>
+        <v>121099960</v>
       </c>
       <c r="B72" t="n">
-        <v>100347</v>
+        <v>91168</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8764,38 +8735,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>5467</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696104</v>
+        <v>695863</v>
       </c>
       <c r="R72" t="n">
-        <v>6603207</v>
+        <v>6603398</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8822,12 +8793,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Undersidan av en kraftigt rötad låga</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8838,26 +8824,46 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121091050</v>
+        <v>121091319</v>
       </c>
       <c r="B73" t="n">
-        <v>8421</v>
+        <v>78604</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8866,50 +8872,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>695927</v>
+        <v>696097</v>
       </c>
       <c r="R73" t="n">
-        <v>6603231</v>
+        <v>6603185</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8936,40 +8933,49 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121093815</v>
+        <v>121090573</v>
       </c>
       <c r="B74" t="n">
-        <v>5189</v>
+        <v>94712</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8982,42 +8988,46 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696247</v>
+        <v>695901</v>
       </c>
       <c r="R74" t="n">
-        <v>6603313</v>
+        <v>6603407</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9044,19 +9054,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>11:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9071,12 +9071,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
         <v>121090765</v>
       </c>
       <c r="B75" t="n">
-        <v>94484</v>
+        <v>94496</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402734</v>
+        <v>121404539</v>
       </c>
       <c r="B76" t="n">
         <v>57367</v>
@@ -9221,19 +9221,19 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696145</v>
+        <v>695869</v>
       </c>
       <c r="R76" t="n">
-        <v>6603212</v>
+        <v>6603281</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9263,19 +9263,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9290,19 +9280,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404558</v>
+        <v>121402709</v>
       </c>
       <c r="B77" t="n">
         <v>57367</v>
@@ -9338,19 +9328,19 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695865</v>
+        <v>696025</v>
       </c>
       <c r="R77" t="n">
-        <v>6603318</v>
+        <v>6603166</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9380,19 +9370,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9407,22 +9387,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402388</v>
+        <v>121402361</v>
       </c>
       <c r="B78" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9431,43 +9411,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695971</v>
+        <v>696010</v>
       </c>
       <c r="R78" t="n">
-        <v>6603090</v>
+        <v>6603109</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9526,10 +9506,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121402709</v>
+        <v>121404293</v>
       </c>
       <c r="B79" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9538,43 +9518,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696025</v>
+        <v>695856</v>
       </c>
       <c r="R79" t="n">
-        <v>6603166</v>
+        <v>6603367</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9633,10 +9613,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121405694</v>
+        <v>121402734</v>
       </c>
       <c r="B80" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9645,40 +9625,31 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9687,10 +9658,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695999</v>
+        <v>696145</v>
       </c>
       <c r="R80" t="n">
-        <v>6603117</v>
+        <v>6603212</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9722,7 +9693,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9732,12 +9703,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9757,17 +9723,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121403961</v>
+        <v>121404815</v>
       </c>
       <c r="B81" t="n">
-        <v>79682</v>
+        <v>94496</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9776,38 +9742,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695886</v>
+        <v>695864</v>
       </c>
       <c r="R81" t="n">
-        <v>6603243</v>
+        <v>6603266</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9837,24 +9803,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9869,22 +9820,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404898</v>
+        <v>121404249</v>
       </c>
       <c r="B82" t="n">
-        <v>8421</v>
+        <v>57367</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9893,43 +9844,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>696024</v>
+        <v>695896</v>
       </c>
       <c r="R82" t="n">
-        <v>6603210</v>
+        <v>6603382</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9988,10 +9939,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121402361</v>
+        <v>121404569</v>
       </c>
       <c r="B83" t="n">
-        <v>5169</v>
+        <v>4772</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10004,21 +9955,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10029,14 +9980,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696010</v>
+        <v>695858</v>
       </c>
       <c r="R83" t="n">
-        <v>6603109</v>
+        <v>6603299</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10095,10 +10046,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404569</v>
+        <v>121402388</v>
       </c>
       <c r="B84" t="n">
-        <v>4772</v>
+        <v>57367</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10107,31 +10058,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10140,10 +10091,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695858</v>
+        <v>695971</v>
       </c>
       <c r="R84" t="n">
-        <v>6603299</v>
+        <v>6603090</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10202,10 +10153,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121405386</v>
+        <v>121404558</v>
       </c>
       <c r="B85" t="n">
-        <v>90662</v>
+        <v>57367</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10214,38 +10165,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>696099</v>
+        <v>695865</v>
       </c>
       <c r="R85" t="n">
-        <v>6603163</v>
+        <v>6603318</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10275,9 +10231,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10292,22 +10258,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404366</v>
+        <v>121405386</v>
       </c>
       <c r="B86" t="n">
-        <v>90697</v>
+        <v>90674</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10316,38 +10282,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695857</v>
+        <v>696099</v>
       </c>
       <c r="R86" t="n">
-        <v>6603366</v>
+        <v>6603163</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10406,10 +10372,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404293</v>
+        <v>121404209</v>
       </c>
       <c r="B87" t="n">
-        <v>5169</v>
+        <v>94496</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10422,39 +10388,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100526</v>
+        <v>2809</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695856</v>
+        <v>695935</v>
       </c>
       <c r="R87" t="n">
-        <v>6603367</v>
+        <v>6603415</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10513,10 +10474,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404545</v>
+        <v>121404366</v>
       </c>
       <c r="B88" t="n">
-        <v>8432</v>
+        <v>90709</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10525,25 +10486,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10553,10 +10514,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695870</v>
+        <v>695857</v>
       </c>
       <c r="R88" t="n">
-        <v>6603295</v>
+        <v>6603366</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10722,10 +10683,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121404539</v>
+        <v>121404545</v>
       </c>
       <c r="B90" t="n">
-        <v>57367</v>
+        <v>8432</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10734,43 +10695,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695869</v>
+        <v>695870</v>
       </c>
       <c r="R90" t="n">
-        <v>6603281</v>
+        <v>6603295</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10829,10 +10785,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121404249</v>
+        <v>121405694</v>
       </c>
       <c r="B91" t="n">
-        <v>57367</v>
+        <v>98094</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10841,43 +10797,52 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695896</v>
+        <v>695999</v>
       </c>
       <c r="R91" t="n">
-        <v>6603382</v>
+        <v>6603117</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10907,9 +10872,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10924,22 +10904,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121404815</v>
+        <v>121403961</v>
       </c>
       <c r="B92" t="n">
-        <v>94484</v>
+        <v>79685</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10948,38 +10928,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695864</v>
+        <v>695886</v>
       </c>
       <c r="R92" t="n">
-        <v>6603266</v>
+        <v>6603243</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11009,9 +10989,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11026,22 +11021,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121404209</v>
+        <v>121404898</v>
       </c>
       <c r="B93" t="n">
-        <v>94484</v>
+        <v>8421</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11054,34 +11049,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2809</v>
+        <v>106554</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>695935</v>
+        <v>696024</v>
       </c>
       <c r="R93" t="n">
-        <v>6603415</v>
+        <v>6603210</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -5831,10 +5831,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121090488</v>
+        <v>121095125</v>
       </c>
       <c r="B46" t="n">
-        <v>79589</v>
+        <v>100361</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5847,37 +5847,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695888</v>
+        <v>696122</v>
       </c>
       <c r="R46" t="n">
-        <v>6603408</v>
+        <v>6603202</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5904,21 +5904,11 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5927,46 +5917,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121091050</v>
+        <v>121095265</v>
       </c>
       <c r="B47" t="n">
-        <v>8421</v>
+        <v>90710</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5975,50 +5945,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695927</v>
+        <v>696112</v>
       </c>
       <c r="R47" t="n">
-        <v>6603231</v>
+        <v>6603209</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6045,37 +6006,46 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121093817</v>
+        <v>121095299</v>
       </c>
       <c r="B48" t="n">
         <v>5169</v>
@@ -6116,14 +6086,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696239</v>
+        <v>696094</v>
       </c>
       <c r="R48" t="n">
-        <v>6603315</v>
+        <v>6603186</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6155,7 +6125,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6165,7 +6135,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6192,10 +6162,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121094501</v>
+        <v>121091186</v>
       </c>
       <c r="B49" t="n">
-        <v>5169</v>
+        <v>90710</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6204,43 +6174,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696380</v>
+        <v>696070</v>
       </c>
       <c r="R49" t="n">
-        <v>6603325</v>
+        <v>6603197</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6272,7 +6237,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6282,7 +6247,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6309,10 +6274,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121090442</v>
+        <v>121092954</v>
       </c>
       <c r="B50" t="n">
-        <v>79589</v>
+        <v>94760</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6325,37 +6290,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>2170</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>695921</v>
+        <v>696174</v>
       </c>
       <c r="R50" t="n">
-        <v>6603409</v>
+        <v>6603210</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6382,9 +6347,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6399,22 +6374,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121090597</v>
+        <v>121090637</v>
       </c>
       <c r="B51" t="n">
-        <v>94712</v>
+        <v>100361</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6427,37 +6402,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695897</v>
+        <v>695859</v>
       </c>
       <c r="R51" t="n">
-        <v>6603417</v>
+        <v>6603407</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6484,19 +6459,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6511,22 +6476,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121092954</v>
+        <v>121094501</v>
       </c>
       <c r="B52" t="n">
-        <v>94759</v>
+        <v>5169</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6539,37 +6504,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696174</v>
+        <v>696380</v>
       </c>
       <c r="R52" t="n">
-        <v>6603210</v>
+        <v>6603325</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6598,7 +6568,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6608,7 +6578,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6635,10 +6605,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121090910</v>
+        <v>121090597</v>
       </c>
       <c r="B53" t="n">
-        <v>100360</v>
+        <v>94713</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6651,37 +6621,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>695893</v>
+        <v>695897</v>
       </c>
       <c r="R53" t="n">
-        <v>6603281</v>
+        <v>6603417</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6708,9 +6678,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6725,22 +6705,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121095299</v>
+        <v>121093800</v>
       </c>
       <c r="B54" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6749,46 +6729,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696094</v>
+        <v>696239</v>
       </c>
       <c r="R54" t="n">
-        <v>6603186</v>
+        <v>6603325</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6817,7 +6797,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6827,7 +6807,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6854,10 +6834,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121090372</v>
+        <v>121095837</v>
       </c>
       <c r="B55" t="n">
-        <v>90709</v>
+        <v>5189</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6866,38 +6846,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>695883</v>
+        <v>695989</v>
       </c>
       <c r="R55" t="n">
-        <v>6603408</v>
+        <v>6603160</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6929,7 +6914,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6939,7 +6924,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6966,10 +6951,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121094438</v>
+        <v>121091126</v>
       </c>
       <c r="B56" t="n">
-        <v>5169</v>
+        <v>78604</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6978,43 +6963,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696484</v>
+        <v>696034</v>
       </c>
       <c r="R56" t="n">
-        <v>6603311</v>
+        <v>6603209</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -7046,7 +7026,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7056,7 +7036,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7083,10 +7063,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121093815</v>
+        <v>121099960</v>
       </c>
       <c r="B57" t="n">
-        <v>5189</v>
+        <v>91169</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7095,46 +7075,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>5467</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696247</v>
+        <v>695863</v>
       </c>
       <c r="R57" t="n">
-        <v>6603313</v>
+        <v>6603398</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7158,22 +7133,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Undersidan av en kraftigt rötad låga</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7184,6 +7164,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7200,10 +7200,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121091204</v>
+        <v>121093973</v>
       </c>
       <c r="B58" t="n">
-        <v>100360</v>
+        <v>91998</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7216,21 +7216,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7240,10 +7240,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696104</v>
+        <v>696429</v>
       </c>
       <c r="R58" t="n">
-        <v>6603207</v>
+        <v>6603315</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7302,10 +7302,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121095556</v>
+        <v>121093980</v>
       </c>
       <c r="B59" t="n">
-        <v>57367</v>
+        <v>100361</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7314,43 +7314,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695980</v>
+        <v>696434</v>
       </c>
       <c r="R59" t="n">
-        <v>6603096</v>
+        <v>6603315</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7409,10 +7404,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121093800</v>
+        <v>121093815</v>
       </c>
       <c r="B60" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7421,20 +7416,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7445,7 +7440,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7454,13 +7449,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696239</v>
+        <v>696247</v>
       </c>
       <c r="R60" t="n">
-        <v>6603325</v>
+        <v>6603313</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7489,7 +7484,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7499,7 +7494,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7526,10 +7521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121093980</v>
+        <v>121091050</v>
       </c>
       <c r="B61" t="n">
-        <v>100360</v>
+        <v>8421</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7542,34 +7537,43 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696434</v>
+        <v>695927</v>
       </c>
       <c r="R61" t="n">
-        <v>6603315</v>
+        <v>6603231</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7610,6 +7614,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7628,10 +7633,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121095265</v>
+        <v>121090372</v>
       </c>
       <c r="B62" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7668,10 +7673,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696112</v>
+        <v>695883</v>
       </c>
       <c r="R62" t="n">
-        <v>6603209</v>
+        <v>6603408</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7703,7 +7708,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7713,7 +7718,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7740,10 +7745,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121095837</v>
+        <v>121090442</v>
       </c>
       <c r="B63" t="n">
-        <v>5189</v>
+        <v>79589</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7756,42 +7761,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105930</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>695989</v>
+        <v>695921</v>
       </c>
       <c r="R63" t="n">
-        <v>6603160</v>
+        <v>6603409</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7818,19 +7818,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7845,22 +7835,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121090637</v>
+        <v>121090488</v>
       </c>
       <c r="B64" t="n">
-        <v>100360</v>
+        <v>79589</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7873,37 +7863,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>695859</v>
+        <v>695888</v>
       </c>
       <c r="R64" t="n">
-        <v>6603407</v>
+        <v>6603408</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7930,11 +7920,21 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7943,26 +7943,46 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121091232</v>
+        <v>121094438</v>
       </c>
       <c r="B65" t="n">
-        <v>90709</v>
+        <v>5169</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7971,41 +7991,46 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696101</v>
+        <v>696484</v>
       </c>
       <c r="R65" t="n">
-        <v>6603200</v>
+        <v>6603311</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8032,9 +8057,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8049,22 +8084,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121095125</v>
+        <v>121091204</v>
       </c>
       <c r="B66" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8101,10 +8136,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696122</v>
+        <v>696104</v>
       </c>
       <c r="R66" t="n">
-        <v>6603202</v>
+        <v>6603207</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8163,10 +8198,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121093973</v>
+        <v>121090910</v>
       </c>
       <c r="B67" t="n">
-        <v>91997</v>
+        <v>100361</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8179,34 +8214,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696429</v>
+        <v>695893</v>
       </c>
       <c r="R67" t="n">
-        <v>6603315</v>
+        <v>6603281</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8265,14 +8300,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121090764</v>
+        <v>121090573</v>
       </c>
       <c r="B68" t="n">
-        <v>94496</v>
+        <v>94713</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8281,37 +8316,46 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2809</v>
+        <v>210</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>695871</v>
+        <v>695901</v>
       </c>
       <c r="R68" t="n">
-        <v>6603412</v>
+        <v>6603407</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8338,24 +8382,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8370,26 +8399,26 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121095510</v>
+        <v>121090764</v>
       </c>
       <c r="B69" t="n">
-        <v>5189</v>
+        <v>94497</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8398,42 +8427,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>105930</v>
+        <v>2809</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696021</v>
+        <v>695871</v>
       </c>
       <c r="R69" t="n">
-        <v>6603152</v>
+        <v>6603412</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8462,7 +8486,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8472,7 +8496,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8499,10 +8528,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121091126</v>
+        <v>121093817</v>
       </c>
       <c r="B70" t="n">
-        <v>78604</v>
+        <v>5169</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8511,38 +8540,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696034</v>
+        <v>696239</v>
       </c>
       <c r="R70" t="n">
-        <v>6603209</v>
+        <v>6603315</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8574,7 +8608,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8584,7 +8618,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8611,10 +8645,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121091186</v>
+        <v>121091232</v>
       </c>
       <c r="B71" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8647,17 +8681,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>696070</v>
+        <v>696101</v>
       </c>
       <c r="R71" t="n">
-        <v>6603197</v>
+        <v>6603200</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8684,19 +8718,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8711,22 +8735,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121099960</v>
+        <v>121091319</v>
       </c>
       <c r="B72" t="n">
-        <v>91168</v>
+        <v>78604</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8739,21 +8763,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8763,13 +8787,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>695863</v>
+        <v>696097</v>
       </c>
       <c r="R72" t="n">
-        <v>6603398</v>
+        <v>6603185</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8793,27 +8817,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Undersidan av en kraftigt rötad låga</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8824,26 +8843,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8860,10 +8859,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121091319</v>
+        <v>121095556</v>
       </c>
       <c r="B73" t="n">
-        <v>78604</v>
+        <v>57367</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8876,37 +8875,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696097</v>
+        <v>695980</v>
       </c>
       <c r="R73" t="n">
-        <v>6603185</v>
+        <v>6603096</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8933,19 +8937,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8960,22 +8954,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121090573</v>
+        <v>121095510</v>
       </c>
       <c r="B74" t="n">
-        <v>94712</v>
+        <v>5189</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8988,46 +8982,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695901</v>
+        <v>696021</v>
       </c>
       <c r="R74" t="n">
-        <v>6603407</v>
+        <v>6603152</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9054,9 +9044,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9071,12 +9071,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
         <v>121090765</v>
       </c>
       <c r="B75" t="n">
-        <v>94496</v>
+        <v>94497</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121404539</v>
+        <v>121404558</v>
       </c>
       <c r="B76" t="n">
         <v>57367</v>
@@ -9221,19 +9221,19 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695869</v>
+        <v>695865</v>
       </c>
       <c r="R76" t="n">
-        <v>6603281</v>
+        <v>6603318</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9263,9 +9263,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9280,22 +9290,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121402709</v>
+        <v>121404293</v>
       </c>
       <c r="B77" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9304,43 +9314,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>696025</v>
+        <v>695856</v>
       </c>
       <c r="R77" t="n">
-        <v>6603166</v>
+        <v>6603367</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9399,10 +9409,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402361</v>
+        <v>121404545</v>
       </c>
       <c r="B78" t="n">
-        <v>5169</v>
+        <v>8432</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9415,39 +9425,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696010</v>
+        <v>695870</v>
       </c>
       <c r="R78" t="n">
-        <v>6603109</v>
+        <v>6603295</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9506,10 +9511,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404293</v>
+        <v>121404815</v>
       </c>
       <c r="B79" t="n">
-        <v>5169</v>
+        <v>94497</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9522,39 +9527,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100526</v>
+        <v>2809</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695856</v>
+        <v>695864</v>
       </c>
       <c r="R79" t="n">
-        <v>6603367</v>
+        <v>6603266</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121402734</v>
+        <v>121402709</v>
       </c>
       <c r="B80" t="n">
         <v>57367</v>
@@ -9649,19 +9649,19 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696145</v>
+        <v>696025</v>
       </c>
       <c r="R80" t="n">
-        <v>6603212</v>
+        <v>6603166</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9691,19 +9691,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9718,22 +9708,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404815</v>
+        <v>121402388</v>
       </c>
       <c r="B81" t="n">
-        <v>94496</v>
+        <v>57367</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9742,38 +9732,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695864</v>
+        <v>695971</v>
       </c>
       <c r="R81" t="n">
-        <v>6603266</v>
+        <v>6603090</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9832,7 +9827,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404249</v>
+        <v>121402734</v>
       </c>
       <c r="B82" t="n">
         <v>57367</v>
@@ -9868,19 +9863,19 @@
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695896</v>
+        <v>696145</v>
       </c>
       <c r="R82" t="n">
-        <v>6603382</v>
+        <v>6603212</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9910,9 +9905,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,22 +9932,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404569</v>
+        <v>121405386</v>
       </c>
       <c r="B83" t="n">
-        <v>4772</v>
+        <v>90675</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9955,39 +9960,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695858</v>
+        <v>696099</v>
       </c>
       <c r="R83" t="n">
-        <v>6603299</v>
+        <v>6603163</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10046,10 +10046,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121402388</v>
+        <v>121405694</v>
       </c>
       <c r="B84" t="n">
-        <v>57367</v>
+        <v>98095</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10058,43 +10058,52 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695971</v>
+        <v>695999</v>
       </c>
       <c r="R84" t="n">
-        <v>6603090</v>
+        <v>6603117</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10124,9 +10133,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10141,22 +10165,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404558</v>
+        <v>121403961</v>
       </c>
       <c r="B85" t="n">
-        <v>57367</v>
+        <v>79685</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10169,39 +10193,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695865</v>
+        <v>695886</v>
       </c>
       <c r="R85" t="n">
-        <v>6603318</v>
+        <v>6603243</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10233,7 +10252,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10243,7 +10262,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10263,17 +10287,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121405386</v>
+        <v>121404569</v>
       </c>
       <c r="B86" t="n">
-        <v>90674</v>
+        <v>4772</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10286,34 +10310,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>696099</v>
+        <v>695858</v>
       </c>
       <c r="R86" t="n">
-        <v>6603163</v>
+        <v>6603299</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10372,10 +10401,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404209</v>
+        <v>121404249</v>
       </c>
       <c r="B87" t="n">
-        <v>94496</v>
+        <v>57367</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10384,38 +10413,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695935</v>
+        <v>695896</v>
       </c>
       <c r="R87" t="n">
-        <v>6603415</v>
+        <v>6603382</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10474,10 +10508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404366</v>
+        <v>121404898</v>
       </c>
       <c r="B88" t="n">
-        <v>90709</v>
+        <v>8421</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10486,38 +10520,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695857</v>
+        <v>696024</v>
       </c>
       <c r="R88" t="n">
-        <v>6603366</v>
+        <v>6603210</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10576,10 +10615,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121402809</v>
+        <v>121404209</v>
       </c>
       <c r="B89" t="n">
-        <v>57367</v>
+        <v>94497</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10588,43 +10627,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>696135</v>
+        <v>695935</v>
       </c>
       <c r="R89" t="n">
-        <v>6603162</v>
+        <v>6603415</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10683,10 +10717,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121404545</v>
+        <v>121404366</v>
       </c>
       <c r="B90" t="n">
-        <v>8432</v>
+        <v>90710</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10695,25 +10729,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10723,10 +10757,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695870</v>
+        <v>695857</v>
       </c>
       <c r="R90" t="n">
-        <v>6603295</v>
+        <v>6603366</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10785,10 +10819,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121405694</v>
+        <v>121402361</v>
       </c>
       <c r="B91" t="n">
-        <v>98094</v>
+        <v>5169</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10797,52 +10831,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695999</v>
+        <v>696010</v>
       </c>
       <c r="R91" t="n">
-        <v>6603117</v>
+        <v>6603109</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10872,24 +10897,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10904,22 +10914,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121403961</v>
+        <v>121402809</v>
       </c>
       <c r="B92" t="n">
-        <v>79685</v>
+        <v>57367</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10932,34 +10942,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695886</v>
+        <v>696135</v>
       </c>
       <c r="R92" t="n">
-        <v>6603243</v>
+        <v>6603162</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10989,24 +11004,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11021,22 +11021,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121404898</v>
+        <v>121404539</v>
       </c>
       <c r="B93" t="n">
-        <v>8421</v>
+        <v>57367</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11045,43 +11045,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>696024</v>
+        <v>695869</v>
       </c>
       <c r="R93" t="n">
-        <v>6603210</v>
+        <v>6603281</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -5831,10 +5831,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121095125</v>
+        <v>121091186</v>
       </c>
       <c r="B46" t="n">
-        <v>100361</v>
+        <v>90713</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5843,41 +5843,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696122</v>
+        <v>696070</v>
       </c>
       <c r="R46" t="n">
-        <v>6603202</v>
+        <v>6603197</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5904,9 +5904,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5921,22 +5931,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121095265</v>
+        <v>121092954</v>
       </c>
       <c r="B47" t="n">
-        <v>90710</v>
+        <v>94763</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5945,41 +5955,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>2170</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696112</v>
+        <v>696174</v>
       </c>
       <c r="R47" t="n">
-        <v>6603209</v>
+        <v>6603210</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6008,7 +6018,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6018,7 +6028,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6045,10 +6055,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121095299</v>
+        <v>121093980</v>
       </c>
       <c r="B48" t="n">
-        <v>5169</v>
+        <v>100364</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6061,42 +6071,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696094</v>
+        <v>696434</v>
       </c>
       <c r="R48" t="n">
-        <v>6603186</v>
+        <v>6603315</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6123,19 +6128,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6150,22 +6145,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121091186</v>
+        <v>121091319</v>
       </c>
       <c r="B49" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6178,21 +6173,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6202,10 +6197,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696070</v>
+        <v>696097</v>
       </c>
       <c r="R49" t="n">
-        <v>6603197</v>
+        <v>6603185</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6237,7 +6232,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6247,7 +6242,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6274,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121092954</v>
+        <v>121095837</v>
       </c>
       <c r="B50" t="n">
-        <v>94760</v>
+        <v>5192</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6290,37 +6285,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2170</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696174</v>
+        <v>695989</v>
       </c>
       <c r="R50" t="n">
-        <v>6603210</v>
+        <v>6603160</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6386,10 +6386,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121090637</v>
+        <v>121091232</v>
       </c>
       <c r="B51" t="n">
-        <v>100361</v>
+        <v>90713</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6398,38 +6398,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695859</v>
+        <v>696101</v>
       </c>
       <c r="R51" t="n">
-        <v>6603407</v>
+        <v>6603200</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6488,10 +6488,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121094501</v>
+        <v>121090910</v>
       </c>
       <c r="B52" t="n">
-        <v>5169</v>
+        <v>100364</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6504,42 +6504,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696380</v>
+        <v>695893</v>
       </c>
       <c r="R52" t="n">
-        <v>6603325</v>
+        <v>6603281</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6566,19 +6561,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6593,22 +6578,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121090597</v>
+        <v>121091204</v>
       </c>
       <c r="B53" t="n">
-        <v>94713</v>
+        <v>100364</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6621,37 +6606,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>695897</v>
+        <v>696104</v>
       </c>
       <c r="R53" t="n">
-        <v>6603417</v>
+        <v>6603207</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6678,19 +6663,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6705,22 +6680,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121093800</v>
+        <v>121090597</v>
       </c>
       <c r="B54" t="n">
-        <v>57367</v>
+        <v>94716</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6729,46 +6704,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696239</v>
+        <v>695897</v>
       </c>
       <c r="R54" t="n">
-        <v>6603325</v>
+        <v>6603417</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6797,7 +6767,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6807,7 +6777,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6834,10 +6804,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121095837</v>
+        <v>121099960</v>
       </c>
       <c r="B55" t="n">
-        <v>5189</v>
+        <v>91172</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6846,46 +6816,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>5467</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>695989</v>
+        <v>695863</v>
       </c>
       <c r="R55" t="n">
-        <v>6603160</v>
+        <v>6603398</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6909,22 +6874,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Undersidan av en kraftigt rötad låga</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6935,6 +6905,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6951,10 +6941,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121091126</v>
+        <v>121090637</v>
       </c>
       <c r="B56" t="n">
-        <v>78604</v>
+        <v>100364</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6963,41 +6953,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696034</v>
+        <v>695859</v>
       </c>
       <c r="R56" t="n">
-        <v>6603209</v>
+        <v>6603407</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7024,19 +7014,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7051,22 +7031,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121099960</v>
+        <v>121090442</v>
       </c>
       <c r="B57" t="n">
-        <v>91169</v>
+        <v>79592</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7075,38 +7055,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5467</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>695863</v>
+        <v>695921</v>
       </c>
       <c r="R57" t="n">
-        <v>6603398</v>
+        <v>6603409</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7133,27 +7113,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Undersidan av en kraftigt rötad låga</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7164,46 +7129,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121093973</v>
+        <v>121093800</v>
       </c>
       <c r="B58" t="n">
-        <v>91998</v>
+        <v>57370</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7212,41 +7157,46 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696429</v>
+        <v>696239</v>
       </c>
       <c r="R58" t="n">
-        <v>6603315</v>
+        <v>6603325</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7273,9 +7223,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7290,26 +7250,26 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121093980</v>
+        <v>121090764</v>
       </c>
       <c r="B59" t="n">
-        <v>100361</v>
+        <v>94500</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7318,37 +7278,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696434</v>
+        <v>695871</v>
       </c>
       <c r="R59" t="n">
-        <v>6603315</v>
+        <v>6603412</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7375,9 +7335,24 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7392,22 +7367,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121093815</v>
+        <v>121091126</v>
       </c>
       <c r="B60" t="n">
-        <v>5189</v>
+        <v>78607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7416,43 +7391,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696247</v>
+        <v>696034</v>
       </c>
       <c r="R60" t="n">
-        <v>6603313</v>
+        <v>6603209</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7484,7 +7454,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7494,7 +7464,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7521,10 +7491,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121091050</v>
+        <v>121093815</v>
       </c>
       <c r="B61" t="n">
-        <v>8421</v>
+        <v>5192</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7537,46 +7507,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695927</v>
+        <v>696247</v>
       </c>
       <c r="R61" t="n">
-        <v>6603231</v>
+        <v>6603313</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7603,40 +7569,49 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121090372</v>
+        <v>121094501</v>
       </c>
       <c r="B62" t="n">
-        <v>90710</v>
+        <v>5172</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7645,38 +7620,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>695883</v>
+        <v>696380</v>
       </c>
       <c r="R62" t="n">
-        <v>6603408</v>
+        <v>6603325</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7708,7 +7688,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7718,7 +7698,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7745,10 +7725,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121090442</v>
+        <v>121094438</v>
       </c>
       <c r="B63" t="n">
-        <v>79589</v>
+        <v>5172</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7761,37 +7741,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>695921</v>
+        <v>696484</v>
       </c>
       <c r="R63" t="n">
-        <v>6603409</v>
+        <v>6603311</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7818,9 +7803,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7835,22 +7830,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121090488</v>
+        <v>121093817</v>
       </c>
       <c r="B64" t="n">
-        <v>79589</v>
+        <v>5172</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7863,34 +7858,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>695888</v>
+        <v>696239</v>
       </c>
       <c r="R64" t="n">
-        <v>6603408</v>
+        <v>6603315</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7943,26 +7943,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7979,10 +7959,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121094438</v>
+        <v>121095265</v>
       </c>
       <c r="B65" t="n">
-        <v>5169</v>
+        <v>90713</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7991,43 +7971,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696484</v>
+        <v>696112</v>
       </c>
       <c r="R65" t="n">
-        <v>6603311</v>
+        <v>6603209</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -8059,7 +8034,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8069,7 +8044,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8096,10 +8071,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121091204</v>
+        <v>121095125</v>
       </c>
       <c r="B66" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8136,10 +8111,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696104</v>
+        <v>696122</v>
       </c>
       <c r="R66" t="n">
-        <v>6603207</v>
+        <v>6603202</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8198,10 +8173,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121090910</v>
+        <v>121090573</v>
       </c>
       <c r="B67" t="n">
-        <v>100361</v>
+        <v>94716</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8214,34 +8189,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>695893</v>
+        <v>695901</v>
       </c>
       <c r="R67" t="n">
-        <v>6603281</v>
+        <v>6603407</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8300,10 +8284,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121090573</v>
+        <v>121095556</v>
       </c>
       <c r="B68" t="n">
-        <v>94713</v>
+        <v>57370</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8312,47 +8296,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>695901</v>
+        <v>695980</v>
       </c>
       <c r="R68" t="n">
-        <v>6603407</v>
+        <v>6603096</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8411,14 +8391,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121090764</v>
+        <v>121091050</v>
       </c>
       <c r="B69" t="n">
-        <v>94497</v>
+        <v>8424</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8427,37 +8407,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2809</v>
+        <v>106554</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695871</v>
+        <v>695927</v>
       </c>
       <c r="R69" t="n">
-        <v>6603412</v>
+        <v>6603231</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8484,54 +8473,40 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121093817</v>
+        <v>121090372</v>
       </c>
       <c r="B70" t="n">
-        <v>5169</v>
+        <v>90713</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8540,43 +8515,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696239</v>
+        <v>695883</v>
       </c>
       <c r="R70" t="n">
-        <v>6603315</v>
+        <v>6603408</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8608,7 +8578,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8618,7 +8588,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8645,10 +8615,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121091232</v>
+        <v>121095299</v>
       </c>
       <c r="B71" t="n">
-        <v>90710</v>
+        <v>5172</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8657,41 +8627,46 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>696101</v>
+        <v>696094</v>
       </c>
       <c r="R71" t="n">
-        <v>6603200</v>
+        <v>6603186</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8718,9 +8693,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8735,22 +8720,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121091319</v>
+        <v>121095510</v>
       </c>
       <c r="B72" t="n">
-        <v>78604</v>
+        <v>5192</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8759,38 +8744,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696097</v>
+        <v>696021</v>
       </c>
       <c r="R72" t="n">
-        <v>6603185</v>
+        <v>6603152</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8822,7 +8812,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8832,7 +8822,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8859,10 +8849,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121095556</v>
+        <v>121093973</v>
       </c>
       <c r="B73" t="n">
-        <v>57367</v>
+        <v>92001</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8871,43 +8861,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>695980</v>
+        <v>696429</v>
       </c>
       <c r="R73" t="n">
-        <v>6603096</v>
+        <v>6603315</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8966,10 +8951,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121095510</v>
+        <v>121090488</v>
       </c>
       <c r="B74" t="n">
-        <v>5189</v>
+        <v>79592</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8982,39 +8967,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>105930</v>
+        <v>6456</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696021</v>
+        <v>695888</v>
       </c>
       <c r="R74" t="n">
-        <v>6603152</v>
+        <v>6603408</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -9046,7 +9026,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9056,7 +9036,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9067,6 +9047,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9086,7 +9086,7 @@
         <v>121090765</v>
       </c>
       <c r="B75" t="n">
-        <v>94497</v>
+        <v>94500</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9185,10 +9185,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121404558</v>
+        <v>121402734</v>
       </c>
       <c r="B76" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695865</v>
+        <v>696145</v>
       </c>
       <c r="R76" t="n">
-        <v>6603318</v>
+        <v>6603212</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9302,10 +9302,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404293</v>
+        <v>121404898</v>
       </c>
       <c r="B77" t="n">
-        <v>5169</v>
+        <v>8424</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9318,21 +9318,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9343,14 +9343,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695856</v>
+        <v>696024</v>
       </c>
       <c r="R77" t="n">
-        <v>6603367</v>
+        <v>6603210</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121404545</v>
+        <v>121404293</v>
       </c>
       <c r="B78" t="n">
-        <v>8432</v>
+        <v>5172</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9425,34 +9425,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695870</v>
+        <v>695856</v>
       </c>
       <c r="R78" t="n">
-        <v>6603295</v>
+        <v>6603367</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9511,10 +9516,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404815</v>
+        <v>121402388</v>
       </c>
       <c r="B79" t="n">
-        <v>94497</v>
+        <v>57370</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9523,38 +9528,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695864</v>
+        <v>695971</v>
       </c>
       <c r="R79" t="n">
-        <v>6603266</v>
+        <v>6603090</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9613,10 +9623,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121402709</v>
+        <v>121404558</v>
       </c>
       <c r="B80" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9649,19 +9659,19 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696025</v>
+        <v>695865</v>
       </c>
       <c r="R80" t="n">
-        <v>6603166</v>
+        <v>6603318</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9691,9 +9701,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9708,22 +9728,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121402388</v>
+        <v>121404545</v>
       </c>
       <c r="B81" t="n">
-        <v>57367</v>
+        <v>8435</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9732,43 +9752,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695971</v>
+        <v>695870</v>
       </c>
       <c r="R81" t="n">
-        <v>6603090</v>
+        <v>6603295</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9827,10 +9842,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121402734</v>
+        <v>121405694</v>
       </c>
       <c r="B82" t="n">
-        <v>57367</v>
+        <v>98098</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9839,31 +9854,40 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9872,10 +9896,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>696145</v>
+        <v>695999</v>
       </c>
       <c r="R82" t="n">
-        <v>6603212</v>
+        <v>6603117</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9907,7 +9931,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9917,7 +9941,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9937,17 +9966,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121405386</v>
+        <v>121404209</v>
       </c>
       <c r="B83" t="n">
-        <v>90675</v>
+        <v>94500</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9960,21 +9989,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9984,10 +10013,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696099</v>
+        <v>695935</v>
       </c>
       <c r="R83" t="n">
-        <v>6603163</v>
+        <v>6603415</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10046,10 +10075,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121405694</v>
+        <v>121404815</v>
       </c>
       <c r="B84" t="n">
-        <v>98095</v>
+        <v>94500</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10058,52 +10087,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695999</v>
+        <v>695864</v>
       </c>
       <c r="R84" t="n">
-        <v>6603117</v>
+        <v>6603266</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10133,24 +10148,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10165,22 +10165,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121403961</v>
+        <v>121402809</v>
       </c>
       <c r="B85" t="n">
-        <v>79685</v>
+        <v>57370</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10193,34 +10193,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695886</v>
+        <v>696135</v>
       </c>
       <c r="R85" t="n">
-        <v>6603243</v>
+        <v>6603162</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10250,24 +10255,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10282,12 +10272,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10297,7 +10287,7 @@
         <v>121404569</v>
       </c>
       <c r="B86" t="n">
-        <v>4772</v>
+        <v>4775</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10401,10 +10391,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404249</v>
+        <v>121402361</v>
       </c>
       <c r="B87" t="n">
-        <v>57367</v>
+        <v>5172</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10413,43 +10403,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695896</v>
+        <v>696010</v>
       </c>
       <c r="R87" t="n">
-        <v>6603382</v>
+        <v>6603109</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10508,10 +10498,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404898</v>
+        <v>121403961</v>
       </c>
       <c r="B88" t="n">
-        <v>8421</v>
+        <v>79688</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10520,43 +10510,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106554</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>696024</v>
+        <v>695886</v>
       </c>
       <c r="R88" t="n">
-        <v>6603210</v>
+        <v>6603243</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10586,9 +10571,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10603,22 +10603,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121404209</v>
+        <v>121404539</v>
       </c>
       <c r="B89" t="n">
-        <v>94497</v>
+        <v>57370</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10627,38 +10627,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>695935</v>
+        <v>695869</v>
       </c>
       <c r="R89" t="n">
-        <v>6603415</v>
+        <v>6603281</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10717,10 +10722,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121404366</v>
+        <v>121405386</v>
       </c>
       <c r="B90" t="n">
-        <v>90710</v>
+        <v>90678</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10729,38 +10734,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695857</v>
+        <v>696099</v>
       </c>
       <c r="R90" t="n">
-        <v>6603366</v>
+        <v>6603163</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10819,10 +10824,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121402361</v>
+        <v>121404249</v>
       </c>
       <c r="B91" t="n">
-        <v>5169</v>
+        <v>57370</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10831,43 +10836,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>696010</v>
+        <v>695896</v>
       </c>
       <c r="R91" t="n">
-        <v>6603109</v>
+        <v>6603382</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10926,10 +10931,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121402809</v>
+        <v>121404366</v>
       </c>
       <c r="B92" t="n">
-        <v>57367</v>
+        <v>90713</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10942,39 +10947,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>696135</v>
+        <v>695857</v>
       </c>
       <c r="R92" t="n">
-        <v>6603162</v>
+        <v>6603366</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11033,10 +11033,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121404539</v>
+        <v>121402709</v>
       </c>
       <c r="B93" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11074,14 +11074,14 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>695869</v>
+        <v>696025</v>
       </c>
       <c r="R93" t="n">
-        <v>6603281</v>
+        <v>6603166</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9185,10 +9185,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402734</v>
+        <v>121402361</v>
       </c>
       <c r="B76" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9197,43 +9197,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696145</v>
+        <v>696010</v>
       </c>
       <c r="R76" t="n">
-        <v>6603212</v>
+        <v>6603109</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9263,19 +9263,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9290,22 +9280,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404898</v>
+        <v>121405386</v>
       </c>
       <c r="B77" t="n">
-        <v>8424</v>
+        <v>90678</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9318,39 +9308,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>696024</v>
+        <v>696099</v>
       </c>
       <c r="R77" t="n">
-        <v>6603210</v>
+        <v>6603163</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9409,10 +9394,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121404293</v>
+        <v>121402388</v>
       </c>
       <c r="B78" t="n">
-        <v>5172</v>
+        <v>57370</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9421,31 +9406,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9454,10 +9439,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695856</v>
+        <v>695971</v>
       </c>
       <c r="R78" t="n">
-        <v>6603367</v>
+        <v>6603090</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9516,10 +9501,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121402388</v>
+        <v>121403961</v>
       </c>
       <c r="B79" t="n">
-        <v>57370</v>
+        <v>79688</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9532,39 +9517,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695971</v>
+        <v>695886</v>
       </c>
       <c r="R79" t="n">
-        <v>6603090</v>
+        <v>6603243</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9594,9 +9574,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9611,22 +9606,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121404558</v>
+        <v>121404209</v>
       </c>
       <c r="B80" t="n">
-        <v>57370</v>
+        <v>94500</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9635,43 +9630,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695865</v>
+        <v>695935</v>
       </c>
       <c r="R80" t="n">
-        <v>6603318</v>
+        <v>6603415</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9701,19 +9691,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9728,22 +9708,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404545</v>
+        <v>121404898</v>
       </c>
       <c r="B81" t="n">
-        <v>8435</v>
+        <v>8424</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9756,34 +9736,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695870</v>
+        <v>696024</v>
       </c>
       <c r="R81" t="n">
-        <v>6603295</v>
+        <v>6603210</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9842,10 +9827,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121405694</v>
+        <v>121402734</v>
       </c>
       <c r="B82" t="n">
-        <v>98098</v>
+        <v>57370</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9854,40 +9839,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9896,10 +9872,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695999</v>
+        <v>696145</v>
       </c>
       <c r="R82" t="n">
-        <v>6603117</v>
+        <v>6603212</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9931,7 +9907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9941,12 +9917,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9966,17 +9937,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404209</v>
+        <v>121402809</v>
       </c>
       <c r="B83" t="n">
-        <v>94500</v>
+        <v>57370</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9985,38 +9956,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695935</v>
+        <v>696135</v>
       </c>
       <c r="R83" t="n">
-        <v>6603415</v>
+        <v>6603162</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10075,10 +10051,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404815</v>
+        <v>121404545</v>
       </c>
       <c r="B84" t="n">
-        <v>94500</v>
+        <v>8435</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10091,21 +10067,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2809</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10115,10 +10091,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695864</v>
+        <v>695870</v>
       </c>
       <c r="R84" t="n">
-        <v>6603266</v>
+        <v>6603295</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10177,7 +10153,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121402809</v>
+        <v>121404558</v>
       </c>
       <c r="B85" t="n">
         <v>57370</v>
@@ -10213,19 +10189,19 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>696135</v>
+        <v>695865</v>
       </c>
       <c r="R85" t="n">
-        <v>6603162</v>
+        <v>6603318</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10255,9 +10231,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10272,22 +10258,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404569</v>
+        <v>121404366</v>
       </c>
       <c r="B86" t="n">
-        <v>4775</v>
+        <v>90713</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10296,43 +10282,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695858</v>
+        <v>695857</v>
       </c>
       <c r="R86" t="n">
-        <v>6603299</v>
+        <v>6603366</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10391,10 +10372,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121402361</v>
+        <v>121404249</v>
       </c>
       <c r="B87" t="n">
-        <v>5172</v>
+        <v>57370</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10403,43 +10384,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>696010</v>
+        <v>695896</v>
       </c>
       <c r="R87" t="n">
-        <v>6603109</v>
+        <v>6603382</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10498,10 +10479,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121403961</v>
+        <v>121402709</v>
       </c>
       <c r="B88" t="n">
-        <v>79688</v>
+        <v>57370</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10514,34 +10495,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695886</v>
+        <v>696025</v>
       </c>
       <c r="R88" t="n">
-        <v>6603243</v>
+        <v>6603166</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10571,24 +10557,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10603,22 +10574,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121404539</v>
+        <v>121405694</v>
       </c>
       <c r="B89" t="n">
-        <v>57370</v>
+        <v>98098</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10627,43 +10598,52 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>695869</v>
+        <v>695999</v>
       </c>
       <c r="R89" t="n">
-        <v>6603281</v>
+        <v>6603117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10693,9 +10673,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10710,22 +10705,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121405386</v>
+        <v>121404815</v>
       </c>
       <c r="B90" t="n">
-        <v>90678</v>
+        <v>94500</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10738,34 +10733,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>696099</v>
+        <v>695864</v>
       </c>
       <c r="R90" t="n">
-        <v>6603163</v>
+        <v>6603266</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10824,7 +10819,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121404249</v>
+        <v>121404539</v>
       </c>
       <c r="B91" t="n">
         <v>57370</v>
@@ -10869,10 +10864,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695896</v>
+        <v>695869</v>
       </c>
       <c r="R91" t="n">
-        <v>6603382</v>
+        <v>6603281</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10931,10 +10926,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121404366</v>
+        <v>121404569</v>
       </c>
       <c r="B92" t="n">
-        <v>90713</v>
+        <v>4775</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10943,38 +10938,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695857</v>
+        <v>695858</v>
       </c>
       <c r="R92" t="n">
-        <v>6603366</v>
+        <v>6603299</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11033,10 +11033,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121402709</v>
+        <v>121404293</v>
       </c>
       <c r="B93" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11045,43 +11045,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>696025</v>
+        <v>695856</v>
       </c>
       <c r="R93" t="n">
-        <v>6603166</v>
+        <v>6603367</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -10153,10 +10153,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404558</v>
+        <v>121404366</v>
       </c>
       <c r="B85" t="n">
-        <v>57370</v>
+        <v>90713</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10169,39 +10169,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695865</v>
+        <v>695857</v>
       </c>
       <c r="R85" t="n">
-        <v>6603318</v>
+        <v>6603366</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10231,19 +10226,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10258,22 +10243,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404366</v>
+        <v>121404558</v>
       </c>
       <c r="B86" t="n">
-        <v>90713</v>
+        <v>57370</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10286,34 +10271,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695857</v>
+        <v>695865</v>
       </c>
       <c r="R86" t="n">
-        <v>6603366</v>
+        <v>6603318</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10343,9 +10333,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10360,12 +10360,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9501,10 +9501,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121403961</v>
+        <v>121404209</v>
       </c>
       <c r="B79" t="n">
-        <v>79688</v>
+        <v>94500</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9513,38 +9513,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695886</v>
+        <v>695935</v>
       </c>
       <c r="R79" t="n">
-        <v>6603243</v>
+        <v>6603415</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9574,24 +9574,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,22 +9591,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121404209</v>
+        <v>121403961</v>
       </c>
       <c r="B80" t="n">
-        <v>94500</v>
+        <v>79688</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9630,38 +9615,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695935</v>
+        <v>695886</v>
       </c>
       <c r="R80" t="n">
-        <v>6603415</v>
+        <v>6603243</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9691,9 +9676,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9708,12 +9708,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9944,10 +9944,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121402809</v>
+        <v>121404545</v>
       </c>
       <c r="B83" t="n">
-        <v>57370</v>
+        <v>8435</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9956,43 +9956,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696135</v>
+        <v>695870</v>
       </c>
       <c r="R83" t="n">
-        <v>6603162</v>
+        <v>6603295</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10051,10 +10046,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404545</v>
+        <v>121402809</v>
       </c>
       <c r="B84" t="n">
-        <v>8435</v>
+        <v>57370</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10063,38 +10058,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695870</v>
+        <v>696135</v>
       </c>
       <c r="R84" t="n">
-        <v>6603295</v>
+        <v>6603162</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10153,10 +10153,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404366</v>
+        <v>121404558</v>
       </c>
       <c r="B85" t="n">
-        <v>90713</v>
+        <v>57370</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10169,34 +10169,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695857</v>
+        <v>695865</v>
       </c>
       <c r="R85" t="n">
-        <v>6603366</v>
+        <v>6603318</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10226,9 +10231,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10243,22 +10258,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404558</v>
+        <v>121404366</v>
       </c>
       <c r="B86" t="n">
-        <v>57370</v>
+        <v>90713</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10271,39 +10286,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695865</v>
+        <v>695857</v>
       </c>
       <c r="R86" t="n">
-        <v>6603318</v>
+        <v>6603366</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10333,19 +10343,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10360,12 +10360,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10819,10 +10819,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121404539</v>
+        <v>121404569</v>
       </c>
       <c r="B91" t="n">
-        <v>57370</v>
+        <v>4775</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10831,31 +10831,31 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10864,10 +10864,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695869</v>
+        <v>695858</v>
       </c>
       <c r="R91" t="n">
-        <v>6603281</v>
+        <v>6603299</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10926,10 +10926,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121404569</v>
+        <v>121404539</v>
       </c>
       <c r="B92" t="n">
-        <v>4775</v>
+        <v>57370</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10938,31 +10938,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695858</v>
+        <v>695869</v>
       </c>
       <c r="R92" t="n">
-        <v>6603299</v>
+        <v>6603281</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9185,10 +9185,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402361</v>
+        <v>121402809</v>
       </c>
       <c r="B76" t="n">
-        <v>5172</v>
+        <v>57371</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9197,31 +9197,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696010</v>
+        <v>696135</v>
       </c>
       <c r="R76" t="n">
-        <v>6603109</v>
+        <v>6603162</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9295,7 +9295,7 @@
         <v>121405386</v>
       </c>
       <c r="B77" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402388</v>
+        <v>121404545</v>
       </c>
       <c r="B78" t="n">
-        <v>57370</v>
+        <v>8435</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9406,43 +9406,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695971</v>
+        <v>695870</v>
       </c>
       <c r="R78" t="n">
-        <v>6603090</v>
+        <v>6603295</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9501,10 +9496,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404209</v>
+        <v>121402709</v>
       </c>
       <c r="B79" t="n">
-        <v>94500</v>
+        <v>57371</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9513,38 +9508,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695935</v>
+        <v>696025</v>
       </c>
       <c r="R79" t="n">
-        <v>6603415</v>
+        <v>6603166</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121403961</v>
+        <v>121404898</v>
       </c>
       <c r="B80" t="n">
-        <v>79688</v>
+        <v>8424</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9615,38 +9615,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>106554</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695886</v>
+        <v>696024</v>
       </c>
       <c r="R80" t="n">
-        <v>6603243</v>
+        <v>6603210</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9676,24 +9681,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9708,22 +9698,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404898</v>
+        <v>121404539</v>
       </c>
       <c r="B81" t="n">
-        <v>8424</v>
+        <v>57371</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9732,43 +9722,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>696024</v>
+        <v>695869</v>
       </c>
       <c r="R81" t="n">
-        <v>6603210</v>
+        <v>6603281</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9827,10 +9817,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121402734</v>
+        <v>121403961</v>
       </c>
       <c r="B82" t="n">
-        <v>57370</v>
+        <v>79689</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9843,39 +9833,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>696145</v>
+        <v>695886</v>
       </c>
       <c r="R82" t="n">
-        <v>6603212</v>
+        <v>6603243</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9907,7 +9892,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9917,7 +9902,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9937,17 +9927,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404545</v>
+        <v>121402361</v>
       </c>
       <c r="B83" t="n">
-        <v>8435</v>
+        <v>5172</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9960,34 +9950,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695870</v>
+        <v>696010</v>
       </c>
       <c r="R83" t="n">
-        <v>6603295</v>
+        <v>6603109</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10046,10 +10041,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121402809</v>
+        <v>121404569</v>
       </c>
       <c r="B84" t="n">
-        <v>57370</v>
+        <v>4775</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10058,43 +10053,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696135</v>
+        <v>695858</v>
       </c>
       <c r="R84" t="n">
-        <v>6603162</v>
+        <v>6603299</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10156,7 +10151,7 @@
         <v>121404558</v>
       </c>
       <c r="B85" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10270,10 +10265,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404366</v>
+        <v>121402388</v>
       </c>
       <c r="B86" t="n">
-        <v>90713</v>
+        <v>57371</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10286,34 +10281,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695857</v>
+        <v>695971</v>
       </c>
       <c r="R86" t="n">
-        <v>6603366</v>
+        <v>6603090</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10372,10 +10372,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404249</v>
+        <v>121402734</v>
       </c>
       <c r="B87" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10408,19 +10408,19 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695896</v>
+        <v>696145</v>
       </c>
       <c r="R87" t="n">
-        <v>6603382</v>
+        <v>6603212</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10450,9 +10450,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10467,22 +10477,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121402709</v>
+        <v>121404366</v>
       </c>
       <c r="B88" t="n">
-        <v>57370</v>
+        <v>90719</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10495,39 +10505,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>696025</v>
+        <v>695857</v>
       </c>
       <c r="R88" t="n">
-        <v>6603166</v>
+        <v>6603366</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10586,10 +10591,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121405694</v>
+        <v>121404209</v>
       </c>
       <c r="B89" t="n">
-        <v>98098</v>
+        <v>94506</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10598,52 +10603,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>695999</v>
+        <v>695935</v>
       </c>
       <c r="R89" t="n">
-        <v>6603117</v>
+        <v>6603415</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10673,24 +10664,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10705,22 +10681,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121404815</v>
+        <v>121404293</v>
       </c>
       <c r="B90" t="n">
-        <v>94500</v>
+        <v>5172</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10733,34 +10709,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695864</v>
+        <v>695856</v>
       </c>
       <c r="R90" t="n">
-        <v>6603266</v>
+        <v>6603367</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10819,10 +10800,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121404569</v>
+        <v>121404815</v>
       </c>
       <c r="B91" t="n">
-        <v>4775</v>
+        <v>94506</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10835,39 +10816,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>102306</v>
+        <v>2809</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695858</v>
+        <v>695864</v>
       </c>
       <c r="R91" t="n">
-        <v>6603299</v>
+        <v>6603266</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10926,10 +10902,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121404539</v>
+        <v>121404249</v>
       </c>
       <c r="B92" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10971,10 +10947,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695869</v>
+        <v>695896</v>
       </c>
       <c r="R92" t="n">
-        <v>6603281</v>
+        <v>6603382</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11033,10 +11009,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121404293</v>
+        <v>121405694</v>
       </c>
       <c r="B93" t="n">
-        <v>5172</v>
+        <v>98104</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11045,43 +11021,52 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>695856</v>
+        <v>695999</v>
       </c>
       <c r="R93" t="n">
-        <v>6603367</v>
+        <v>6603117</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11111,9 +11096,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11128,12 +11128,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9185,10 +9185,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402809</v>
+        <v>121402709</v>
       </c>
       <c r="B76" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696135</v>
+        <v>696025</v>
       </c>
       <c r="R76" t="n">
-        <v>6603162</v>
+        <v>6603166</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9292,10 +9292,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121405386</v>
+        <v>121404293</v>
       </c>
       <c r="B77" t="n">
-        <v>90684</v>
+        <v>5172</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9308,34 +9308,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>696099</v>
+        <v>695856</v>
       </c>
       <c r="R77" t="n">
-        <v>6603163</v>
+        <v>6603367</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9394,10 +9399,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121404545</v>
+        <v>121404249</v>
       </c>
       <c r="B78" t="n">
-        <v>8435</v>
+        <v>57372</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9406,38 +9411,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695870</v>
+        <v>695896</v>
       </c>
       <c r="R78" t="n">
-        <v>6603295</v>
+        <v>6603382</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9496,10 +9506,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121402709</v>
+        <v>121402361</v>
       </c>
       <c r="B79" t="n">
-        <v>57371</v>
+        <v>5172</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9508,31 +9518,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9541,10 +9551,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696025</v>
+        <v>696010</v>
       </c>
       <c r="R79" t="n">
-        <v>6603166</v>
+        <v>6603109</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9603,10 +9613,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121404898</v>
+        <v>121402388</v>
       </c>
       <c r="B80" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9615,43 +9625,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696024</v>
+        <v>695971</v>
       </c>
       <c r="R80" t="n">
-        <v>6603210</v>
+        <v>6603090</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9710,10 +9720,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404539</v>
+        <v>121402734</v>
       </c>
       <c r="B81" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9746,19 +9756,19 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695869</v>
+        <v>696145</v>
       </c>
       <c r="R81" t="n">
-        <v>6603281</v>
+        <v>6603212</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9788,9 +9798,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9805,22 +9825,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121403961</v>
+        <v>121404569</v>
       </c>
       <c r="B82" t="n">
-        <v>79689</v>
+        <v>4775</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9829,38 +9849,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>102306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695886</v>
+        <v>695858</v>
       </c>
       <c r="R82" t="n">
-        <v>6603243</v>
+        <v>6603299</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9890,24 +9915,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9922,22 +9932,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121402361</v>
+        <v>121403961</v>
       </c>
       <c r="B83" t="n">
-        <v>5172</v>
+        <v>79690</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9946,43 +9956,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696010</v>
+        <v>695886</v>
       </c>
       <c r="R83" t="n">
-        <v>6603109</v>
+        <v>6603243</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10012,9 +10017,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10029,22 +10049,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404569</v>
+        <v>121404539</v>
       </c>
       <c r="B84" t="n">
-        <v>4775</v>
+        <v>57372</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10053,31 +10073,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10086,10 +10106,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695858</v>
+        <v>695869</v>
       </c>
       <c r="R84" t="n">
-        <v>6603299</v>
+        <v>6603281</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10151,7 +10171,7 @@
         <v>121404558</v>
       </c>
       <c r="B85" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10265,10 +10285,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121402388</v>
+        <v>121405386</v>
       </c>
       <c r="B86" t="n">
-        <v>57371</v>
+        <v>90685</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10277,43 +10297,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695971</v>
+        <v>696099</v>
       </c>
       <c r="R86" t="n">
-        <v>6603090</v>
+        <v>6603163</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10372,10 +10387,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121402734</v>
+        <v>121404815</v>
       </c>
       <c r="B87" t="n">
-        <v>57371</v>
+        <v>94507</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10384,43 +10399,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>696145</v>
+        <v>695864</v>
       </c>
       <c r="R87" t="n">
-        <v>6603212</v>
+        <v>6603266</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10450,19 +10460,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10477,22 +10477,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404366</v>
+        <v>121404545</v>
       </c>
       <c r="B88" t="n">
-        <v>90719</v>
+        <v>8435</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10501,25 +10501,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10529,10 +10529,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695857</v>
+        <v>695870</v>
       </c>
       <c r="R88" t="n">
-        <v>6603366</v>
+        <v>6603295</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10591,10 +10591,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121404209</v>
+        <v>121402809</v>
       </c>
       <c r="B89" t="n">
-        <v>94506</v>
+        <v>57372</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10603,38 +10603,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>695935</v>
+        <v>696135</v>
       </c>
       <c r="R89" t="n">
-        <v>6603415</v>
+        <v>6603162</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10693,10 +10698,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121404293</v>
+        <v>121405694</v>
       </c>
       <c r="B90" t="n">
-        <v>5172</v>
+        <v>98105</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10705,43 +10710,52 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695856</v>
+        <v>695999</v>
       </c>
       <c r="R90" t="n">
-        <v>6603367</v>
+        <v>6603117</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10771,9 +10785,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10788,22 +10817,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121404815</v>
+        <v>121404366</v>
       </c>
       <c r="B91" t="n">
-        <v>94506</v>
+        <v>90720</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10812,25 +10841,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10840,10 +10869,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695864</v>
+        <v>695857</v>
       </c>
       <c r="R91" t="n">
-        <v>6603266</v>
+        <v>6603366</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10902,10 +10931,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121404249</v>
+        <v>121404209</v>
       </c>
       <c r="B92" t="n">
-        <v>57371</v>
+        <v>94507</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10914,43 +10943,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695896</v>
+        <v>695935</v>
       </c>
       <c r="R92" t="n">
-        <v>6603382</v>
+        <v>6603415</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11009,10 +11033,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121405694</v>
+        <v>121404898</v>
       </c>
       <c r="B93" t="n">
-        <v>98104</v>
+        <v>8424</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11021,52 +11045,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>695999</v>
+        <v>696024</v>
       </c>
       <c r="R93" t="n">
-        <v>6603117</v>
+        <v>6603210</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11096,24 +11111,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11128,12 +11128,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9185,10 +9185,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402709</v>
+        <v>121404569</v>
       </c>
       <c r="B76" t="n">
-        <v>57372</v>
+        <v>4775</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9197,43 +9197,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696025</v>
+        <v>695858</v>
       </c>
       <c r="R76" t="n">
-        <v>6603166</v>
+        <v>6603299</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9399,7 +9399,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121404249</v>
+        <v>121402734</v>
       </c>
       <c r="B78" t="n">
         <v>57372</v>
@@ -9435,19 +9435,19 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695896</v>
+        <v>696145</v>
       </c>
       <c r="R78" t="n">
-        <v>6603382</v>
+        <v>6603212</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9477,9 +9477,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9494,22 +9504,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121402361</v>
+        <v>121404545</v>
       </c>
       <c r="B79" t="n">
-        <v>5172</v>
+        <v>8435</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9522,39 +9532,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696010</v>
+        <v>695870</v>
       </c>
       <c r="R79" t="n">
-        <v>6603109</v>
+        <v>6603295</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9613,10 +9618,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121402388</v>
+        <v>121405386</v>
       </c>
       <c r="B80" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9625,43 +9630,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695971</v>
+        <v>696099</v>
       </c>
       <c r="R80" t="n">
-        <v>6603090</v>
+        <v>6603163</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9720,10 +9720,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121402734</v>
+        <v>121404815</v>
       </c>
       <c r="B81" t="n">
-        <v>57372</v>
+        <v>94507</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9732,43 +9732,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>696145</v>
+        <v>695864</v>
       </c>
       <c r="R81" t="n">
-        <v>6603212</v>
+        <v>6603266</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9798,19 +9793,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9825,22 +9810,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404569</v>
+        <v>121403961</v>
       </c>
       <c r="B82" t="n">
-        <v>4775</v>
+        <v>79690</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9849,43 +9834,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102306</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695858</v>
+        <v>695886</v>
       </c>
       <c r="R82" t="n">
-        <v>6603299</v>
+        <v>6603243</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9915,9 +9895,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9932,22 +9927,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121403961</v>
+        <v>121402388</v>
       </c>
       <c r="B83" t="n">
-        <v>79690</v>
+        <v>57372</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9960,34 +9955,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695886</v>
+        <v>695971</v>
       </c>
       <c r="R83" t="n">
-        <v>6603243</v>
+        <v>6603090</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10017,24 +10017,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10049,19 +10034,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404539</v>
+        <v>121404558</v>
       </c>
       <c r="B84" t="n">
         <v>57372</v>
@@ -10097,19 +10082,19 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695869</v>
+        <v>695865</v>
       </c>
       <c r="R84" t="n">
-        <v>6603281</v>
+        <v>6603318</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10139,9 +10124,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10156,22 +10151,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404558</v>
+        <v>121405694</v>
       </c>
       <c r="B85" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10180,31 +10175,40 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10213,10 +10217,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695865</v>
+        <v>695999</v>
       </c>
       <c r="R85" t="n">
-        <v>6603318</v>
+        <v>6603117</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10248,7 +10252,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10258,7 +10262,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10278,17 +10287,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121405386</v>
+        <v>121402361</v>
       </c>
       <c r="B86" t="n">
-        <v>90685</v>
+        <v>5172</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10301,34 +10310,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>696099</v>
+        <v>696010</v>
       </c>
       <c r="R86" t="n">
-        <v>6603163</v>
+        <v>6603109</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10387,10 +10401,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404815</v>
+        <v>121404898</v>
       </c>
       <c r="B87" t="n">
-        <v>94507</v>
+        <v>8424</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10403,34 +10417,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2809</v>
+        <v>106554</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695864</v>
+        <v>696024</v>
       </c>
       <c r="R87" t="n">
-        <v>6603266</v>
+        <v>6603210</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10489,10 +10508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404545</v>
+        <v>121402809</v>
       </c>
       <c r="B88" t="n">
-        <v>8435</v>
+        <v>57372</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10501,38 +10520,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695870</v>
+        <v>696135</v>
       </c>
       <c r="R88" t="n">
-        <v>6603295</v>
+        <v>6603162</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10591,10 +10615,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121402809</v>
+        <v>121404209</v>
       </c>
       <c r="B89" t="n">
-        <v>57372</v>
+        <v>94507</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10603,43 +10627,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>696135</v>
+        <v>695935</v>
       </c>
       <c r="R89" t="n">
-        <v>6603162</v>
+        <v>6603415</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10698,10 +10717,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121405694</v>
+        <v>121404366</v>
       </c>
       <c r="B90" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10710,52 +10729,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695999</v>
+        <v>695857</v>
       </c>
       <c r="R90" t="n">
-        <v>6603117</v>
+        <v>6603366</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10785,24 +10790,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10817,22 +10807,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121404366</v>
+        <v>121404539</v>
       </c>
       <c r="B91" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10845,34 +10835,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695857</v>
+        <v>695869</v>
       </c>
       <c r="R91" t="n">
-        <v>6603366</v>
+        <v>6603281</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10931,10 +10926,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121404209</v>
+        <v>121404249</v>
       </c>
       <c r="B92" t="n">
-        <v>94507</v>
+        <v>57372</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10943,38 +10938,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695935</v>
+        <v>695896</v>
       </c>
       <c r="R92" t="n">
-        <v>6603415</v>
+        <v>6603382</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11033,10 +11033,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121404898</v>
+        <v>121402709</v>
       </c>
       <c r="B93" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11045,31 +11045,31 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11078,10 +11078,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>696024</v>
+        <v>696025</v>
       </c>
       <c r="R93" t="n">
-        <v>6603210</v>
+        <v>6603166</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9185,10 +9185,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121404569</v>
+        <v>121402809</v>
       </c>
       <c r="B76" t="n">
-        <v>4775</v>
+        <v>57372</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9197,43 +9197,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695858</v>
+        <v>696135</v>
       </c>
       <c r="R76" t="n">
-        <v>6603299</v>
+        <v>6603162</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9292,10 +9292,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404293</v>
+        <v>121404558</v>
       </c>
       <c r="B77" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9304,43 +9304,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695856</v>
+        <v>695865</v>
       </c>
       <c r="R77" t="n">
-        <v>6603367</v>
+        <v>6603318</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9370,9 +9370,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9387,12 +9397,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9516,10 +9526,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404545</v>
+        <v>121405694</v>
       </c>
       <c r="B79" t="n">
-        <v>8435</v>
+        <v>98105</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9528,38 +9538,52 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695870</v>
+        <v>695999</v>
       </c>
       <c r="R79" t="n">
-        <v>6603295</v>
+        <v>6603117</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9589,9 +9613,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,22 +9645,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121405386</v>
+        <v>121402709</v>
       </c>
       <c r="B80" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9630,38 +9669,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696099</v>
+        <v>696025</v>
       </c>
       <c r="R80" t="n">
-        <v>6603163</v>
+        <v>6603166</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9720,10 +9764,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404815</v>
+        <v>121404249</v>
       </c>
       <c r="B81" t="n">
-        <v>94507</v>
+        <v>57372</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9732,38 +9776,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695864</v>
+        <v>695896</v>
       </c>
       <c r="R81" t="n">
-        <v>6603266</v>
+        <v>6603382</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9822,10 +9871,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121403961</v>
+        <v>121404545</v>
       </c>
       <c r="B82" t="n">
-        <v>79690</v>
+        <v>8435</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9834,38 +9883,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695886</v>
+        <v>695870</v>
       </c>
       <c r="R82" t="n">
-        <v>6603243</v>
+        <v>6603295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9895,24 +9944,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,22 +9961,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121402388</v>
+        <v>121402361</v>
       </c>
       <c r="B83" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9951,43 +9985,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695971</v>
+        <v>696010</v>
       </c>
       <c r="R83" t="n">
-        <v>6603090</v>
+        <v>6603109</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10046,7 +10080,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404558</v>
+        <v>121404539</v>
       </c>
       <c r="B84" t="n">
         <v>57372</v>
@@ -10082,19 +10116,19 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695865</v>
+        <v>695869</v>
       </c>
       <c r="R84" t="n">
-        <v>6603318</v>
+        <v>6603281</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10124,19 +10158,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10151,22 +10175,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121405694</v>
+        <v>121405386</v>
       </c>
       <c r="B85" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10175,52 +10199,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695999</v>
+        <v>696099</v>
       </c>
       <c r="R85" t="n">
-        <v>6603117</v>
+        <v>6603163</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10250,24 +10260,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10282,22 +10277,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121402361</v>
+        <v>121404569</v>
       </c>
       <c r="B86" t="n">
-        <v>5172</v>
+        <v>4775</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10310,21 +10305,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10335,14 +10330,14 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>696010</v>
+        <v>695858</v>
       </c>
       <c r="R86" t="n">
-        <v>6603109</v>
+        <v>6603299</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10508,10 +10503,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121402809</v>
+        <v>121403961</v>
       </c>
       <c r="B88" t="n">
-        <v>57372</v>
+        <v>79690</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10524,39 +10519,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>696135</v>
+        <v>695886</v>
       </c>
       <c r="R88" t="n">
-        <v>6603162</v>
+        <v>6603243</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10586,9 +10576,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10603,22 +10608,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121404209</v>
+        <v>121404293</v>
       </c>
       <c r="B89" t="n">
-        <v>94507</v>
+        <v>5172</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10631,34 +10636,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>695935</v>
+        <v>695856</v>
       </c>
       <c r="R89" t="n">
-        <v>6603415</v>
+        <v>6603367</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10717,10 +10727,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121404366</v>
+        <v>121404815</v>
       </c>
       <c r="B90" t="n">
-        <v>90720</v>
+        <v>94507</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10729,25 +10739,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10757,10 +10767,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695857</v>
+        <v>695864</v>
       </c>
       <c r="R90" t="n">
-        <v>6603366</v>
+        <v>6603266</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10819,10 +10829,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121404539</v>
+        <v>121404209</v>
       </c>
       <c r="B91" t="n">
-        <v>57372</v>
+        <v>94507</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10831,43 +10841,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695869</v>
+        <v>695935</v>
       </c>
       <c r="R91" t="n">
-        <v>6603281</v>
+        <v>6603415</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10926,10 +10931,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121404249</v>
+        <v>121404366</v>
       </c>
       <c r="B92" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10942,39 +10947,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695896</v>
+        <v>695857</v>
       </c>
       <c r="R92" t="n">
-        <v>6603382</v>
+        <v>6603366</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11033,7 +11033,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121402709</v>
+        <v>121402388</v>
       </c>
       <c r="B93" t="n">
         <v>57372</v>
@@ -11069,19 +11069,19 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>696025</v>
+        <v>695971</v>
       </c>
       <c r="R93" t="n">
-        <v>6603166</v>
+        <v>6603090</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9185,7 +9185,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402809</v>
+        <v>121404539</v>
       </c>
       <c r="B76" t="n">
         <v>57372</v>
@@ -9226,14 +9226,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696135</v>
+        <v>695869</v>
       </c>
       <c r="R76" t="n">
-        <v>6603162</v>
+        <v>6603281</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9292,10 +9292,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404558</v>
+        <v>121404898</v>
       </c>
       <c r="B77" t="n">
-        <v>57372</v>
+        <v>8424</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9304,43 +9304,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695865</v>
+        <v>696024</v>
       </c>
       <c r="R77" t="n">
-        <v>6603318</v>
+        <v>6603210</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9370,19 +9370,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9397,22 +9387,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402734</v>
+        <v>121404815</v>
       </c>
       <c r="B78" t="n">
-        <v>57372</v>
+        <v>94507</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9421,43 +9411,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696145</v>
+        <v>695864</v>
       </c>
       <c r="R78" t="n">
-        <v>6603212</v>
+        <v>6603266</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9487,19 +9472,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9514,22 +9489,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121405694</v>
+        <v>121402809</v>
       </c>
       <c r="B79" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9538,52 +9513,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695999</v>
+        <v>696135</v>
       </c>
       <c r="R79" t="n">
-        <v>6603117</v>
+        <v>6603162</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9613,24 +9579,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9645,22 +9596,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121402709</v>
+        <v>121405386</v>
       </c>
       <c r="B80" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9669,43 +9620,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696025</v>
+        <v>696099</v>
       </c>
       <c r="R80" t="n">
-        <v>6603166</v>
+        <v>6603163</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9764,7 +9710,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404249</v>
+        <v>121402709</v>
       </c>
       <c r="B81" t="n">
         <v>57372</v>
@@ -9805,14 +9751,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695896</v>
+        <v>696025</v>
       </c>
       <c r="R81" t="n">
-        <v>6603382</v>
+        <v>6603166</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9871,10 +9817,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404545</v>
+        <v>121404569</v>
       </c>
       <c r="B82" t="n">
-        <v>8435</v>
+        <v>4775</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9887,34 +9833,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695870</v>
+        <v>695858</v>
       </c>
       <c r="R82" t="n">
-        <v>6603295</v>
+        <v>6603299</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9973,10 +9924,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121402361</v>
+        <v>121404366</v>
       </c>
       <c r="B83" t="n">
-        <v>5172</v>
+        <v>90720</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9985,43 +9936,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696010</v>
+        <v>695857</v>
       </c>
       <c r="R83" t="n">
-        <v>6603109</v>
+        <v>6603366</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10080,7 +10026,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404539</v>
+        <v>121402734</v>
       </c>
       <c r="B84" t="n">
         <v>57372</v>
@@ -10116,19 +10062,19 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695869</v>
+        <v>696145</v>
       </c>
       <c r="R84" t="n">
-        <v>6603281</v>
+        <v>6603212</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10158,9 +10104,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10175,22 +10131,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121405386</v>
+        <v>121405694</v>
       </c>
       <c r="B85" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10199,38 +10155,52 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>696099</v>
+        <v>695999</v>
       </c>
       <c r="R85" t="n">
-        <v>6603163</v>
+        <v>6603117</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10260,9 +10230,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10277,22 +10262,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404569</v>
+        <v>121402388</v>
       </c>
       <c r="B86" t="n">
-        <v>4775</v>
+        <v>57372</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10301,31 +10286,31 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10334,10 +10319,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695858</v>
+        <v>695971</v>
       </c>
       <c r="R86" t="n">
-        <v>6603299</v>
+        <v>6603090</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10396,10 +10381,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404898</v>
+        <v>121404209</v>
       </c>
       <c r="B87" t="n">
-        <v>8424</v>
+        <v>94507</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10412,39 +10397,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106554</v>
+        <v>2809</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>696024</v>
+        <v>695935</v>
       </c>
       <c r="R87" t="n">
-        <v>6603210</v>
+        <v>6603415</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10503,10 +10483,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121403961</v>
+        <v>121404249</v>
       </c>
       <c r="B88" t="n">
-        <v>79690</v>
+        <v>57372</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10519,34 +10499,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695886</v>
+        <v>695896</v>
       </c>
       <c r="R88" t="n">
-        <v>6603243</v>
+        <v>6603382</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10576,24 +10561,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10608,22 +10578,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121404293</v>
+        <v>121404558</v>
       </c>
       <c r="B89" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10632,43 +10602,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>695856</v>
+        <v>695865</v>
       </c>
       <c r="R89" t="n">
-        <v>6603367</v>
+        <v>6603318</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10698,9 +10668,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10715,22 +10695,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121404815</v>
+        <v>121402361</v>
       </c>
       <c r="B90" t="n">
-        <v>94507</v>
+        <v>5172</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10743,34 +10723,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695864</v>
+        <v>696010</v>
       </c>
       <c r="R90" t="n">
-        <v>6603266</v>
+        <v>6603109</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10829,10 +10814,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121404209</v>
+        <v>121404293</v>
       </c>
       <c r="B91" t="n">
-        <v>94507</v>
+        <v>5172</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10845,34 +10830,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695935</v>
+        <v>695856</v>
       </c>
       <c r="R91" t="n">
-        <v>6603415</v>
+        <v>6603367</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10931,10 +10921,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121404366</v>
+        <v>121403961</v>
       </c>
       <c r="B92" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10947,34 +10937,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695857</v>
+        <v>695886</v>
       </c>
       <c r="R92" t="n">
-        <v>6603366</v>
+        <v>6603243</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11004,9 +10994,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11021,22 +11026,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121402388</v>
+        <v>121404545</v>
       </c>
       <c r="B93" t="n">
-        <v>57372</v>
+        <v>8435</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11045,43 +11050,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>695971</v>
+        <v>695870</v>
       </c>
       <c r="R93" t="n">
-        <v>6603090</v>
+        <v>6603295</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9924,10 +9924,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404366</v>
+        <v>121402734</v>
       </c>
       <c r="B83" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9940,34 +9940,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695857</v>
+        <v>696145</v>
       </c>
       <c r="R83" t="n">
-        <v>6603366</v>
+        <v>6603212</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9997,9 +10002,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10014,22 +10029,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121402734</v>
+        <v>121404366</v>
       </c>
       <c r="B84" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10042,39 +10057,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696145</v>
+        <v>695857</v>
       </c>
       <c r="R84" t="n">
-        <v>6603212</v>
+        <v>6603366</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10104,19 +10114,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10131,12 +10131,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9924,10 +9924,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121402734</v>
+        <v>121404366</v>
       </c>
       <c r="B83" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9940,39 +9940,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696145</v>
+        <v>695857</v>
       </c>
       <c r="R83" t="n">
-        <v>6603212</v>
+        <v>6603366</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10002,19 +9997,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10029,22 +10014,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404366</v>
+        <v>121402734</v>
       </c>
       <c r="B84" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10057,34 +10042,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695857</v>
+        <v>696145</v>
       </c>
       <c r="R84" t="n">
-        <v>6603366</v>
+        <v>6603212</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10114,9 +10104,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10131,12 +10131,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9185,10 +9185,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121404539</v>
+        <v>121404569</v>
       </c>
       <c r="B76" t="n">
-        <v>57372</v>
+        <v>4776</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9197,31 +9197,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695869</v>
+        <v>695858</v>
       </c>
       <c r="R76" t="n">
-        <v>6603281</v>
+        <v>6603299</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9292,10 +9292,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404898</v>
+        <v>121402361</v>
       </c>
       <c r="B77" t="n">
-        <v>8424</v>
+        <v>5173</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9308,21 +9308,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>696024</v>
+        <v>696010</v>
       </c>
       <c r="R77" t="n">
-        <v>6603210</v>
+        <v>6603109</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121404815</v>
+        <v>121404209</v>
       </c>
       <c r="B78" t="n">
-        <v>94507</v>
+        <v>94515</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9435,14 +9435,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695864</v>
+        <v>695935</v>
       </c>
       <c r="R78" t="n">
-        <v>6603266</v>
+        <v>6603415</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121402809</v>
+        <v>121402734</v>
       </c>
       <c r="B79" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9537,19 +9537,19 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696135</v>
+        <v>696145</v>
       </c>
       <c r="R79" t="n">
-        <v>6603162</v>
+        <v>6603212</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9579,9 +9579,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9596,22 +9606,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121405386</v>
+        <v>121404366</v>
       </c>
       <c r="B80" t="n">
-        <v>90685</v>
+        <v>90728</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9620,38 +9630,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696099</v>
+        <v>695857</v>
       </c>
       <c r="R80" t="n">
-        <v>6603163</v>
+        <v>6603366</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9710,10 +9720,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121402709</v>
+        <v>121403961</v>
       </c>
       <c r="B81" t="n">
-        <v>57372</v>
+        <v>79697</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9726,39 +9736,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>696025</v>
+        <v>695886</v>
       </c>
       <c r="R81" t="n">
-        <v>6603166</v>
+        <v>6603243</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9788,9 +9793,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9805,22 +9825,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404569</v>
+        <v>121404545</v>
       </c>
       <c r="B82" t="n">
-        <v>4775</v>
+        <v>8436</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9833,39 +9853,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695858</v>
+        <v>695870</v>
       </c>
       <c r="R82" t="n">
-        <v>6603299</v>
+        <v>6603295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9924,10 +9939,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404366</v>
+        <v>121404539</v>
       </c>
       <c r="B83" t="n">
-        <v>90720</v>
+        <v>57373</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9940,34 +9955,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695857</v>
+        <v>695869</v>
       </c>
       <c r="R83" t="n">
-        <v>6603366</v>
+        <v>6603281</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10026,10 +10046,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121402734</v>
+        <v>121402709</v>
       </c>
       <c r="B84" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10062,19 +10082,19 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696145</v>
+        <v>696025</v>
       </c>
       <c r="R84" t="n">
-        <v>6603212</v>
+        <v>6603166</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10104,19 +10124,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10131,22 +10141,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121405694</v>
+        <v>121404815</v>
       </c>
       <c r="B85" t="n">
-        <v>98105</v>
+        <v>94515</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10155,52 +10165,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695999</v>
+        <v>695864</v>
       </c>
       <c r="R85" t="n">
-        <v>6603117</v>
+        <v>6603266</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10230,24 +10226,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10262,22 +10243,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121402388</v>
+        <v>121404249</v>
       </c>
       <c r="B86" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10310,7 +10291,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10319,10 +10300,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695971</v>
+        <v>695896</v>
       </c>
       <c r="R86" t="n">
-        <v>6603090</v>
+        <v>6603382</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10381,10 +10362,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404209</v>
+        <v>121404558</v>
       </c>
       <c r="B87" t="n">
-        <v>94507</v>
+        <v>57373</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10393,38 +10374,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695935</v>
+        <v>695865</v>
       </c>
       <c r="R87" t="n">
-        <v>6603415</v>
+        <v>6603318</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10454,9 +10440,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10471,22 +10467,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404249</v>
+        <v>121402809</v>
       </c>
       <c r="B88" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10524,14 +10520,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695896</v>
+        <v>696135</v>
       </c>
       <c r="R88" t="n">
-        <v>6603382</v>
+        <v>6603162</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10590,10 +10586,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121404558</v>
+        <v>121404898</v>
       </c>
       <c r="B89" t="n">
-        <v>57372</v>
+        <v>8425</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10602,43 +10598,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>695865</v>
+        <v>696024</v>
       </c>
       <c r="R89" t="n">
-        <v>6603318</v>
+        <v>6603210</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10668,19 +10664,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10695,22 +10681,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121402361</v>
+        <v>121405694</v>
       </c>
       <c r="B90" t="n">
-        <v>5172</v>
+        <v>98113</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10719,43 +10705,52 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>696010</v>
+        <v>695999</v>
       </c>
       <c r="R90" t="n">
-        <v>6603109</v>
+        <v>6603117</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10785,9 +10780,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10802,22 +10812,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121404293</v>
+        <v>121405386</v>
       </c>
       <c r="B91" t="n">
-        <v>5172</v>
+        <v>90693</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10830,39 +10840,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695856</v>
+        <v>696099</v>
       </c>
       <c r="R91" t="n">
-        <v>6603367</v>
+        <v>6603163</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10921,10 +10926,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121403961</v>
+        <v>121402388</v>
       </c>
       <c r="B92" t="n">
-        <v>79690</v>
+        <v>57373</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10937,34 +10942,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695886</v>
+        <v>695971</v>
       </c>
       <c r="R92" t="n">
-        <v>6603243</v>
+        <v>6603090</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10994,24 +11004,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11026,22 +11021,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121404545</v>
+        <v>121404293</v>
       </c>
       <c r="B93" t="n">
-        <v>8435</v>
+        <v>5173</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11054,34 +11049,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>695870</v>
+        <v>695856</v>
       </c>
       <c r="R93" t="n">
-        <v>6603295</v>
+        <v>6603367</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -9837,10 +9837,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404545</v>
+        <v>121404539</v>
       </c>
       <c r="B82" t="n">
-        <v>8436</v>
+        <v>57373</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9849,38 +9849,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695870</v>
+        <v>695869</v>
       </c>
       <c r="R82" t="n">
-        <v>6603295</v>
+        <v>6603281</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9939,7 +9944,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404539</v>
+        <v>121402709</v>
       </c>
       <c r="B83" t="n">
         <v>57373</v>
@@ -9980,14 +9985,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695869</v>
+        <v>696025</v>
       </c>
       <c r="R83" t="n">
-        <v>6603281</v>
+        <v>6603166</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10046,10 +10051,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121402709</v>
+        <v>121404545</v>
       </c>
       <c r="B84" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10058,43 +10063,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696025</v>
+        <v>695870</v>
       </c>
       <c r="R84" t="n">
-        <v>6603166</v>
+        <v>6603295</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10586,10 +10586,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121404898</v>
+        <v>121405386</v>
       </c>
       <c r="B89" t="n">
-        <v>8425</v>
+        <v>90693</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10602,39 +10602,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>696024</v>
+        <v>696099</v>
       </c>
       <c r="R89" t="n">
-        <v>6603210</v>
+        <v>6603163</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10693,10 +10688,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121405694</v>
+        <v>121404898</v>
       </c>
       <c r="B90" t="n">
-        <v>98113</v>
+        <v>8425</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10705,52 +10700,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695999</v>
+        <v>696024</v>
       </c>
       <c r="R90" t="n">
-        <v>6603117</v>
+        <v>6603210</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10780,24 +10766,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10812,22 +10783,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121405386</v>
+        <v>121405694</v>
       </c>
       <c r="B91" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10836,38 +10807,52 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>696099</v>
+        <v>695999</v>
       </c>
       <c r="R91" t="n">
-        <v>6603163</v>
+        <v>6603117</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10897,9 +10882,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10914,12 +10914,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 52356-2023 artfynd.xlsx
+++ b/artfynd/A 52356-2023 artfynd.xlsx
@@ -10586,10 +10586,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121405386</v>
+        <v>121404898</v>
       </c>
       <c r="B89" t="n">
-        <v>90693</v>
+        <v>8425</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10602,34 +10602,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>696099</v>
+        <v>696024</v>
       </c>
       <c r="R89" t="n">
-        <v>6603163</v>
+        <v>6603210</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10688,10 +10693,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121404898</v>
+        <v>121405694</v>
       </c>
       <c r="B90" t="n">
-        <v>8425</v>
+        <v>98113</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10700,43 +10705,52 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>696024</v>
+        <v>695999</v>
       </c>
       <c r="R90" t="n">
-        <v>6603210</v>
+        <v>6603117</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10766,9 +10780,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10783,22 +10812,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121405694</v>
+        <v>121405386</v>
       </c>
       <c r="B91" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10807,52 +10836,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695999</v>
+        <v>696099</v>
       </c>
       <c r="R91" t="n">
-        <v>6603117</v>
+        <v>6603163</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10882,24 +10897,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10914,12 +10914,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
